--- a/research/traditional_assets/database/data/singapore/singapore_chemical_specialty.xlsx
+++ b/research/traditional_assets/database/data/singapore/singapore_chemical_specialty.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.377</v>
+        <v>-0.3255</v>
       </c>
       <c r="G2">
-        <v>-0.3542695836273819</v>
+        <v>-0.4765264586160108</v>
       </c>
       <c r="H2">
-        <v>-0.354034344860033</v>
+        <v>-0.4762550881953867</v>
       </c>
       <c r="I2">
-        <v>-0.529287226534933</v>
+        <v>-0.4199457259158751</v>
       </c>
       <c r="J2">
-        <v>-0.529287226534933</v>
+        <v>-0.4199457259158751</v>
       </c>
       <c r="K2">
-        <v>-8.99</v>
+        <v>-56.43</v>
       </c>
       <c r="L2">
-        <v>-0.5286991296165608</v>
+        <v>-3.828358208955224</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>6.206</v>
+        <v>6.908</v>
       </c>
       <c r="V2">
-        <v>0.3859452736318408</v>
+        <v>0.3698072805139186</v>
       </c>
       <c r="W2">
-        <v>-0.2735055643879173</v>
+        <v>-0.7749809275565021</v>
       </c>
       <c r="X2">
-        <v>0.09702189910952452</v>
+        <v>0.1343830282500496</v>
       </c>
       <c r="Y2">
-        <v>-0.3705274634974419</v>
+        <v>-0.9093639558065516</v>
       </c>
       <c r="Z2">
-        <v>0.2397495911116124</v>
+        <v>0.2162431782172408</v>
       </c>
       <c r="AA2">
-        <v>-0.2114814956295862</v>
+        <v>-0.1928069174517924</v>
       </c>
       <c r="AB2">
-        <v>0.06904826532590916</v>
+        <v>0.1025921833999307</v>
       </c>
       <c r="AC2">
-        <v>-0.2805297609554953</v>
+        <v>-0.2953991008517231</v>
       </c>
       <c r="AD2">
-        <v>17.75</v>
+        <v>11.08</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>17.75</v>
+        <v>11.08</v>
       </c>
       <c r="AG2">
-        <v>11.544</v>
+        <v>4.172</v>
       </c>
       <c r="AH2">
-        <v>0.5246822347029264</v>
+        <v>0.3723118279569892</v>
       </c>
       <c r="AI2">
-        <v>0.2176845719892078</v>
+        <v>0.8501496201948899</v>
       </c>
       <c r="AJ2">
-        <v>0.417897480451781</v>
+        <v>0.1825660773674077</v>
       </c>
       <c r="AK2">
-        <v>0.1532375819683012</v>
+        <v>0.681142857142857</v>
       </c>
       <c r="AL2">
-        <v>0.907</v>
+        <v>0.8220000000000001</v>
       </c>
       <c r="AM2">
-        <v>0.8110000000000001</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="AN2">
-        <v>-2.238335435056747</v>
+        <v>-2.078799249530957</v>
       </c>
       <c r="AO2">
-        <v>-9.922822491730981</v>
+        <v>-7.530413625304135</v>
       </c>
       <c r="AP2">
-        <v>-1.455737704918033</v>
+        <v>-0.7827392120075046</v>
       </c>
       <c r="AQ2">
-        <v>-11.09741060419235</v>
+        <v>-7.623152709359605</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.508</v>
+        <v>-0.435</v>
       </c>
       <c r="G3">
-        <v>-2.475124378109453</v>
+        <v>-1.9375</v>
       </c>
       <c r="H3">
-        <v>-2.475124378109453</v>
+        <v>-1.9375</v>
       </c>
       <c r="I3">
-        <v>-4.402985074626866</v>
+        <v>-0.9305555555555557</v>
       </c>
       <c r="J3">
-        <v>-4.402985074626866</v>
+        <v>-0.9305555555555557</v>
       </c>
       <c r="K3">
-        <v>-3.73</v>
+        <v>-52.8</v>
       </c>
       <c r="L3">
-        <v>-4.639303482587064</v>
+        <v>-36.66666666666666</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.516</v>
+        <v>0.798</v>
       </c>
       <c r="V3">
-        <v>0.05645514223194748</v>
+        <v>0.06091603053435115</v>
       </c>
       <c r="W3">
-        <v>-0.07313725490196078</v>
+        <v>-1.079754601226994</v>
       </c>
       <c r="X3">
-        <v>0.08066348668138629</v>
+        <v>0.1214100327740045</v>
       </c>
       <c r="Y3">
-        <v>-0.1538007415833471</v>
+        <v>-1.201164634000998</v>
       </c>
       <c r="Z3">
-        <v>0.01442566476477554</v>
+        <v>0.02630905835495304</v>
       </c>
       <c r="AA3">
-        <v>-0.06351598665087738</v>
+        <v>-0.02448204041363686</v>
       </c>
       <c r="AB3">
-        <v>0.07919346584954115</v>
+        <v>0.1075160705219872</v>
       </c>
       <c r="AC3">
-        <v>-0.1427094525004185</v>
+        <v>-0.1319981109356241</v>
       </c>
       <c r="AD3">
-        <v>6.35</v>
+        <v>5.75</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>6.35</v>
+        <v>5.75</v>
       </c>
       <c r="AG3">
-        <v>5.834</v>
+        <v>4.952</v>
       </c>
       <c r="AH3">
-        <v>0.4099418979987088</v>
+        <v>0.3050397877984085</v>
       </c>
       <c r="AI3">
-        <v>0.1021721641190668</v>
+        <v>1.120202610559127</v>
       </c>
       <c r="AJ3">
-        <v>0.3896086550020034</v>
+        <v>0.2743186350542876</v>
       </c>
       <c r="AK3">
-        <v>0.09465554726287438</v>
+        <v>1.142329873125721</v>
       </c>
       <c r="AL3">
-        <v>0.41</v>
+        <v>0.336</v>
       </c>
       <c r="AM3">
-        <v>0.33</v>
+        <v>0.335</v>
       </c>
       <c r="AN3">
-        <v>-1.873156342182891</v>
+        <v>-4.914529914529915</v>
       </c>
       <c r="AO3">
-        <v>-8.634146341463415</v>
+        <v>-3.988095238095238</v>
       </c>
       <c r="AP3">
-        <v>-1.72094395280236</v>
+        <v>-4.232478632478633</v>
       </c>
       <c r="AQ3">
-        <v>-10.72727272727273</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="4">
@@ -844,25 +844,25 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.246</v>
+        <v>-0.216</v>
       </c>
       <c r="G4">
-        <v>-0.2490123456790123</v>
+        <v>-0.3183458646616541</v>
       </c>
       <c r="H4">
-        <v>-0.2487654320987654</v>
+        <v>-0.3180451127819549</v>
       </c>
       <c r="I4">
-        <v>-0.337037037037037</v>
+        <v>-0.3646616541353383</v>
       </c>
       <c r="J4">
-        <v>-0.337037037037037</v>
+        <v>-0.3646616541353383</v>
       </c>
       <c r="K4">
-        <v>-5.26</v>
+        <v>-3.63</v>
       </c>
       <c r="L4">
-        <v>-0.3246913580246913</v>
+        <v>-0.2729323308270676</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -886,73 +886,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>5.69</v>
+        <v>6.11</v>
       </c>
       <c r="V4">
-        <v>0.8198847262247839</v>
+        <v>1.094982078853047</v>
       </c>
       <c r="W4">
-        <v>-0.4738738738738739</v>
+        <v>-0.4702072538860104</v>
       </c>
       <c r="X4">
-        <v>0.1133803115376627</v>
+        <v>0.1473560237260946</v>
       </c>
       <c r="Y4">
-        <v>-0.5872541854115366</v>
+        <v>-0.6175632776121049</v>
       </c>
       <c r="Z4">
-        <v>1.066491112574062</v>
+        <v>0.9903201787043933</v>
       </c>
       <c r="AA4">
-        <v>-0.3594470046082949</v>
+        <v>-0.3611317944899479</v>
       </c>
       <c r="AB4">
-        <v>0.05890306480227716</v>
+        <v>0.09766829627787423</v>
       </c>
       <c r="AC4">
-        <v>-0.4183500694105721</v>
+        <v>-0.4588000907678221</v>
       </c>
       <c r="AD4">
-        <v>11.4</v>
+        <v>5.33</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>11.4</v>
+        <v>5.33</v>
       </c>
       <c r="AG4">
-        <v>5.71</v>
+        <v>-0.7800000000000002</v>
       </c>
       <c r="AH4">
-        <v>0.6215921483097055</v>
+        <v>0.4885426214482126</v>
       </c>
       <c r="AI4">
-        <v>0.5879319236719959</v>
+        <v>0.6746835443037974</v>
       </c>
       <c r="AJ4">
-        <v>0.4513833992094862</v>
+        <v>-0.1625000000000001</v>
       </c>
       <c r="AK4">
-        <v>0.4167883211678832</v>
+        <v>-0.4357541899441343</v>
       </c>
       <c r="AL4">
-        <v>0.497</v>
+        <v>0.486</v>
       </c>
       <c r="AM4">
-        <v>0.481</v>
+        <v>0.477</v>
       </c>
       <c r="AN4">
-        <v>-2.511013215859031</v>
+        <v>-1.28125</v>
       </c>
       <c r="AO4">
-        <v>-10.98591549295775</v>
+        <v>-9.979423868312757</v>
       </c>
       <c r="AP4">
-        <v>-1.257709251101321</v>
+        <v>0.1875000000000001</v>
       </c>
       <c r="AQ4">
-        <v>-11.35135135135135</v>
+        <v>-10.16771488469602</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/singapore/singapore_chemical_specialty.xlsx
+++ b/research/traditional_assets/database/data/singapore/singapore_chemical_specialty.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="sgx_mzh" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -351,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,115 +590,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.3255</v>
+        <v>-0.347</v>
+      </c>
+      <c r="F2">
+        <v>-0.14</v>
       </c>
       <c r="G2">
-        <v>-0.4765264586160108</v>
+        <v>0.401178731582319</v>
       </c>
       <c r="H2">
-        <v>-0.4762550881953867</v>
+        <v>0.3121716848174247</v>
       </c>
       <c r="I2">
-        <v>-0.4199457259158751</v>
+        <v>0.04977578475336323</v>
       </c>
       <c r="J2">
-        <v>-0.4199457259158751</v>
+        <v>0.0482289526846028</v>
       </c>
       <c r="K2">
-        <v>-56.43</v>
+        <v>18.299</v>
       </c>
       <c r="L2">
-        <v>-3.828358208955224</v>
+        <v>0.117226137091608</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>26.8</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.05795471747075232</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>1.464560904967484</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.02292238825335726</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0.579266626591617</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>16.2</v>
+      </c>
+      <c r="T2">
+        <v>0.6044776119402984</v>
       </c>
       <c r="U2">
-        <v>6.908</v>
+        <v>101.655</v>
       </c>
       <c r="V2">
-        <v>0.3698072805139186</v>
+        <v>0.219827865839154</v>
       </c>
       <c r="W2">
-        <v>-0.7749809275565021</v>
+        <v>0.04170739654610623</v>
       </c>
       <c r="X2">
-        <v>0.1343830282500496</v>
+        <v>0.09106170671580942</v>
       </c>
       <c r="Y2">
-        <v>-0.9093639558065516</v>
+        <v>-0.04935431016970319</v>
       </c>
       <c r="Z2">
-        <v>0.2162431782172408</v>
+        <v>0.6580888862657145</v>
       </c>
       <c r="AA2">
-        <v>-0.1928069174517924</v>
+        <v>-0.4728403141361257</v>
       </c>
       <c r="AB2">
-        <v>0.1025921833999307</v>
+        <v>0.08147394091890443</v>
       </c>
       <c r="AC2">
-        <v>-0.2953991008517231</v>
+        <v>-0.5543142550550301</v>
       </c>
       <c r="AD2">
-        <v>11.08</v>
+        <v>38.76</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>11.08</v>
+        <v>38.76</v>
       </c>
       <c r="AG2">
-        <v>4.172</v>
+        <v>-62.89499999999999</v>
       </c>
       <c r="AH2">
-        <v>0.3723118279569892</v>
+        <v>0.07733594046170114</v>
       </c>
       <c r="AI2">
-        <v>0.8501496201948899</v>
+        <v>0.1084104830363886</v>
       </c>
       <c r="AJ2">
-        <v>0.1825660773674077</v>
+        <v>-0.1574205013327993</v>
       </c>
       <c r="AK2">
-        <v>0.681142857142857</v>
+        <v>-0.2458036150464093</v>
       </c>
       <c r="AL2">
-        <v>0.8220000000000001</v>
+        <v>1.597</v>
       </c>
       <c r="AM2">
-        <v>0.8120000000000001</v>
+        <v>-0.06700000000000017</v>
       </c>
       <c r="AN2">
-        <v>-2.078799249530957</v>
+        <v>1.264187866927593</v>
       </c>
       <c r="AO2">
-        <v>-7.530413625304135</v>
+        <v>4.865372573575454</v>
       </c>
       <c r="AP2">
-        <v>-0.7827392120075046</v>
+        <v>-2.051369863013698</v>
       </c>
       <c r="AQ2">
-        <v>-7.623152709359605</v>
+        <v>-115.970149253731</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +715,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AsiaPhos Limited (Catalist:5WV)</t>
+          <t>Nanofilm Technologies International Limited (SGX:MZH)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -715,116 +723,119 @@
           <t>Chemical (Specialty)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>-0.435</v>
+      <c r="F3">
+        <v>-0.14</v>
       </c>
       <c r="G3">
-        <v>-1.9375</v>
+        <v>0.484375</v>
       </c>
       <c r="H3">
-        <v>-1.9375</v>
+        <v>0.3899456521739131</v>
       </c>
       <c r="I3">
-        <v>-0.9305555555555557</v>
+        <v>0.1080163043478261</v>
       </c>
       <c r="J3">
-        <v>-0.9305555555555557</v>
+        <v>0.09852630046583852</v>
       </c>
       <c r="K3">
-        <v>-52.8</v>
+        <v>12.8</v>
       </c>
       <c r="L3">
-        <v>-36.66666666666666</v>
+        <v>0.08695652173913045</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>26.8</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.05975473801560757</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>2.09375</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>10.6</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.02363433667781494</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>0.8281249999999999</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>16.2</v>
+      </c>
+      <c r="T3">
+        <v>0.6044776119402984</v>
       </c>
       <c r="U3">
-        <v>0.798</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="V3">
-        <v>0.06091603053435115</v>
+        <v>0.2098104793756967</v>
       </c>
       <c r="W3">
-        <v>-1.079754601226994</v>
+        <v>0.04170739654610623</v>
       </c>
       <c r="X3">
-        <v>0.1214100327740045</v>
+        <v>0.08455191245970203</v>
       </c>
       <c r="Y3">
-        <v>-1.201164634000998</v>
+        <v>-0.0428445159135958</v>
       </c>
       <c r="Z3">
-        <v>0.02630905835495304</v>
+        <v>0.6453309951775537</v>
       </c>
       <c r="AA3">
-        <v>-0.02448204041363686</v>
+        <v>0.06358207553078224</v>
       </c>
       <c r="AB3">
-        <v>0.1075160705219872</v>
+        <v>0.08154375255421782</v>
       </c>
       <c r="AC3">
-        <v>-0.1319981109356241</v>
+        <v>-0.01796167702343558</v>
       </c>
       <c r="AD3">
-        <v>5.75</v>
+        <v>34.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>5.75</v>
+        <v>34.3</v>
       </c>
       <c r="AG3">
-        <v>4.952</v>
+        <v>-59.8</v>
       </c>
       <c r="AH3">
-        <v>0.3050397877984085</v>
+        <v>0.07104391052195526</v>
       </c>
       <c r="AI3">
-        <v>1.120202610559127</v>
+        <v>0.09970930232558138</v>
       </c>
       <c r="AJ3">
-        <v>0.2743186350542876</v>
+        <v>-0.1538461538461539</v>
       </c>
       <c r="AK3">
-        <v>1.142329873125721</v>
+        <v>-0.2392957182873149</v>
       </c>
       <c r="AL3">
-        <v>0.336</v>
+        <v>1.24</v>
       </c>
       <c r="AM3">
-        <v>0.335</v>
+        <v>-0.3300000000000001</v>
       </c>
       <c r="AN3">
-        <v>-4.914529914529915</v>
+        <v>0.88860103626943</v>
       </c>
       <c r="AO3">
-        <v>-3.988095238095238</v>
+        <v>12.82258064516129</v>
       </c>
       <c r="AP3">
-        <v>-4.232478632478633</v>
+        <v>-1.549222797927461</v>
       </c>
       <c r="AQ3">
-        <v>-4</v>
+        <v>-48.18181818181817</v>
       </c>
     </row>
     <row r="4">
@@ -835,7 +846,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Matex International Limited (Catalist:M15)</t>
+          <t>AsiaPhos Limited (Catalist:5WV)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -844,25 +855,25 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.216</v>
+        <v>-0.423</v>
       </c>
       <c r="G4">
-        <v>-0.3183458646616541</v>
+        <v>-1.933333333333333</v>
       </c>
       <c r="H4">
-        <v>-0.3180451127819549</v>
+        <v>-1.933333333333333</v>
       </c>
       <c r="I4">
-        <v>-0.3646616541353383</v>
+        <v>-1.926666666666667</v>
       </c>
       <c r="J4">
-        <v>-0.3646616541353383</v>
+        <v>-1.926666666666667</v>
       </c>
       <c r="K4">
-        <v>-3.63</v>
+        <v>-0.601</v>
       </c>
       <c r="L4">
-        <v>-0.2729323308270676</v>
+        <v>-0.4006666666666667</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -886,73 +897,8973 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>6.11</v>
+        <v>0.415</v>
       </c>
       <c r="V4">
-        <v>1.094982078853047</v>
+        <v>0.06629392971246006</v>
       </c>
       <c r="W4">
-        <v>-0.4702072538860104</v>
+        <v>-0.5181034482758621</v>
       </c>
       <c r="X4">
-        <v>0.1473560237260946</v>
+        <v>0.09106170671580942</v>
       </c>
       <c r="Y4">
-        <v>-0.6175632776121049</v>
+        <v>-0.6091651549916715</v>
       </c>
       <c r="Z4">
-        <v>0.9903201787043933</v>
+        <v>0.2454188481675393</v>
       </c>
       <c r="AA4">
-        <v>-0.3611317944899479</v>
+        <v>-0.4728403141361257</v>
       </c>
       <c r="AB4">
-        <v>0.09766829627787423</v>
+        <v>0.08147394091890443</v>
       </c>
       <c r="AC4">
-        <v>-0.4588000907678221</v>
+        <v>-0.5543142550550301</v>
       </c>
       <c r="AD4">
-        <v>5.33</v>
+        <v>1.62</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>5.33</v>
+        <v>1.62</v>
       </c>
       <c r="AG4">
-        <v>-0.7800000000000002</v>
+        <v>1.205</v>
       </c>
       <c r="AH4">
-        <v>0.4885426214482126</v>
+        <v>0.2055837563451777</v>
       </c>
       <c r="AI4">
-        <v>0.6746835443037974</v>
+        <v>-162.0000000000035</v>
       </c>
       <c r="AJ4">
-        <v>-0.1625000000000001</v>
+        <v>0.1614199598124582</v>
       </c>
       <c r="AK4">
-        <v>-0.4357541899441343</v>
+        <v>-2.83529411764706</v>
       </c>
       <c r="AL4">
-        <v>0.486</v>
+        <v>0.215</v>
       </c>
       <c r="AM4">
-        <v>0.477</v>
+        <v>0.205</v>
       </c>
       <c r="AN4">
-        <v>-1.28125</v>
+        <v>-0.5704225352112676</v>
       </c>
       <c r="AO4">
-        <v>-9.979423868312757</v>
+        <v>-13.44186046511628</v>
       </c>
       <c r="AP4">
-        <v>0.1875000000000001</v>
+        <v>-0.4242957746478874</v>
       </c>
       <c r="AQ4">
-        <v>-10.16771488469602</v>
+        <v>-14.09756097560976</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Matex International Limited (Catalist:M15)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Chemical (Specialty)</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>-0.271</v>
+      </c>
+      <c r="G5">
+        <v>-0.7805405405405405</v>
+      </c>
+      <c r="H5">
+        <v>-0.7797297297297296</v>
+      </c>
+      <c r="I5">
+        <v>-0.7081081081081081</v>
+      </c>
+      <c r="J5">
+        <v>-0.7043049699315683</v>
+      </c>
+      <c r="K5">
+        <v>6.1</v>
+      </c>
+      <c r="L5">
+        <v>0.8243243243243242</v>
+      </c>
+      <c r="M5">
+        <v>-0</v>
+      </c>
+      <c r="N5">
+        <v>-0</v>
+      </c>
+      <c r="O5">
+        <v>-0</v>
+      </c>
+      <c r="P5">
+        <v>-0</v>
+      </c>
+      <c r="Q5">
+        <v>-0</v>
+      </c>
+      <c r="R5">
+        <v>-0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>7.14</v>
+      </c>
+      <c r="V5">
+        <v>0.9308996088657105</v>
+      </c>
+      <c r="W5">
+        <v>1.618037135278515</v>
+      </c>
+      <c r="X5">
+        <v>0.09504266095127806</v>
+      </c>
+      <c r="Y5">
+        <v>1.522994474327237</v>
+      </c>
+      <c r="Z5">
+        <v>2.474916387959867</v>
+      </c>
+      <c r="AA5">
+        <v>-1.74309591220522</v>
+      </c>
+      <c r="AB5">
+        <v>0.08076618606054259</v>
+      </c>
+      <c r="AC5">
+        <v>-1.823862098265763</v>
+      </c>
+      <c r="AD5">
+        <v>2.84</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>2.84</v>
+      </c>
+      <c r="AG5">
+        <v>-4.3</v>
+      </c>
+      <c r="AH5">
+        <v>0.2702188392007612</v>
+      </c>
+      <c r="AI5">
+        <v>0.2097488921713442</v>
+      </c>
+      <c r="AJ5">
+        <v>-1.275964391691395</v>
+      </c>
+      <c r="AK5">
+        <v>-0.671875</v>
+      </c>
+      <c r="AL5">
+        <v>0.142</v>
+      </c>
+      <c r="AM5">
+        <v>0.05799999999999998</v>
+      </c>
+      <c r="AN5">
+        <v>-0.5568627450980392</v>
+      </c>
+      <c r="AO5">
+        <v>-36.90140845070423</v>
+      </c>
+      <c r="AP5">
+        <v>0.8431372549019608</v>
+      </c>
+      <c r="AQ5">
+        <v>-90.34482758620693</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Nanofilm Technologies International Limited (SGX:MZH)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SGX:MZH</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Chemical (Specialty)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>12.8225806451613</v>
+      </c>
+      <c r="F2">
+        <v>10.2722680806131</v>
+      </c>
+      <c r="G2">
+        <v>0.88860103626943</v>
+      </c>
+      <c r="H2">
+        <v>0.875544041450777</v>
+      </c>
+      <c r="I2">
+        <v>0.0710439105219553</v>
+      </c>
+      <c r="J2">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="K2">
+        <v>448.5</v>
+      </c>
+      <c r="L2">
+        <v>451.655693519881</v>
+      </c>
+      <c r="M2">
+        <v>388.7</v>
+      </c>
+      <c r="N2">
+        <v>391.351693519881</v>
+      </c>
+      <c r="O2">
+        <v>34.3</v>
+      </c>
+      <c r="P2">
+        <v>33.796</v>
+      </c>
+      <c r="Q2">
+        <v>0.08154375255421779</v>
+      </c>
+      <c r="R2">
+        <v>0.0812541324157588</v>
+      </c>
+      <c r="S2">
+        <v>0.04220965</v>
+      </c>
+      <c r="T2">
+        <v>0.038014</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.08455191245970201</v>
+      </c>
+      <c r="X2">
+        <v>0.0845087660384503</v>
+      </c>
+      <c r="Y2">
+        <v>0.994606792602218</v>
+      </c>
+      <c r="Z2">
+        <v>0.993668826922833</v>
+      </c>
+      <c r="AA2">
+        <v>34.3</v>
+      </c>
+      <c r="AB2">
+        <v>0.050855</v>
+      </c>
+      <c r="AC2">
+        <v>12.82258064516129</v>
+      </c>
+      <c r="AD2">
+        <v>34.3</v>
+      </c>
+      <c r="AE2">
+        <v>1.24</v>
+      </c>
+      <c r="AF2">
+        <v>22.7</v>
+      </c>
+      <c r="AG2">
+        <v>38.6</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>448.5</v>
+      </c>
+      <c r="AK2">
+        <v>0.046</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.17</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>57.90000000000001</v>
+      </c>
+      <c r="AR2">
+        <v>1.24</v>
+      </c>
+      <c r="AS2">
+        <v>34.3</v>
+      </c>
+      <c r="AT2">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.08182110354797975</v>
+      </c>
+      <c r="C2">
+        <v>480.2941058600454</v>
+      </c>
+      <c r="D2">
+        <v>386.1941058600455</v>
+      </c>
+      <c r="E2">
+        <v>-34.3</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H2">
+        <v>448.5</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>38.6</v>
+      </c>
+      <c r="K2">
+        <v>22.7</v>
+      </c>
+      <c r="L2">
+        <v>15.9</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>15.9</v>
+      </c>
+      <c r="O2">
+        <v>2.703</v>
+      </c>
+      <c r="P2">
+        <v>13.197</v>
+      </c>
+      <c r="Q2">
+        <v>35.89700000000001</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.08182110354797975</v>
+      </c>
+      <c r="T2">
+        <v>0.9352413814778209</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.17</v>
+      </c>
+      <c r="W2">
+        <v>0.037101</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.0817309776719482</v>
+      </c>
+      <c r="C3">
+        <v>476.2768510141583</v>
+      </c>
+      <c r="D3">
+        <v>387.0048510141582</v>
+      </c>
+      <c r="E3">
+        <v>-29.472</v>
+      </c>
+      <c r="F3">
+        <v>4.828</v>
+      </c>
+      <c r="G3">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H3">
+        <v>448.5</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>38.6</v>
+      </c>
+      <c r="K3">
+        <v>22.7</v>
+      </c>
+      <c r="L3">
+        <v>15.9</v>
+      </c>
+      <c r="M3">
+        <v>0.2158116</v>
+      </c>
+      <c r="N3">
+        <v>15.6841884</v>
+      </c>
+      <c r="O3">
+        <v>2.666312028</v>
+      </c>
+      <c r="P3">
+        <v>13.017876372</v>
+      </c>
+      <c r="Q3">
+        <v>35.717876372</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.0821817855272204</v>
+      </c>
+      <c r="T3">
+        <v>0.9430822940700087</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0.17</v>
+      </c>
+      <c r="W3">
+        <v>0.037101</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>73.67537240815599</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.08164085179591661</v>
+      </c>
+      <c r="C4">
+        <v>472.2630073570872</v>
+      </c>
+      <c r="D4">
+        <v>387.8190073570872</v>
+      </c>
+      <c r="E4">
+        <v>-24.644</v>
+      </c>
+      <c r="F4">
+        <v>9.656000000000001</v>
+      </c>
+      <c r="G4">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H4">
+        <v>448.5</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>38.6</v>
+      </c>
+      <c r="K4">
+        <v>22.7</v>
+      </c>
+      <c r="L4">
+        <v>15.9</v>
+      </c>
+      <c r="M4">
+        <v>0.4316232</v>
+      </c>
+      <c r="N4">
+        <v>15.4683768</v>
+      </c>
+      <c r="O4">
+        <v>2.629624056</v>
+      </c>
+      <c r="P4">
+        <v>12.838752744</v>
+      </c>
+      <c r="Q4">
+        <v>35.538752744</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.08254982836318023</v>
+      </c>
+      <c r="T4">
+        <v>0.9510832252865269</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.17</v>
+      </c>
+      <c r="W4">
+        <v>0.037101</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>36.83768620407799</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.08155072591988506</v>
+      </c>
+      <c r="C5">
+        <v>468.2525964629482</v>
+      </c>
+      <c r="D5">
+        <v>388.6365964629482</v>
+      </c>
+      <c r="E5">
+        <v>-19.816</v>
+      </c>
+      <c r="F5">
+        <v>14.484</v>
+      </c>
+      <c r="G5">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H5">
+        <v>448.5</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>38.6</v>
+      </c>
+      <c r="K5">
+        <v>22.7</v>
+      </c>
+      <c r="L5">
+        <v>15.9</v>
+      </c>
+      <c r="M5">
+        <v>0.6474348000000001</v>
+      </c>
+      <c r="N5">
+        <v>15.2525652</v>
+      </c>
+      <c r="O5">
+        <v>2.592936084</v>
+      </c>
+      <c r="P5">
+        <v>12.659629116</v>
+      </c>
+      <c r="Q5">
+        <v>35.359629116</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.08292545971122171</v>
+      </c>
+      <c r="T5">
+        <v>0.9592491241569938</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.17</v>
+      </c>
+      <c r="W5">
+        <v>0.037101</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>24.55845746938533</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.08146060004385351</v>
+      </c>
+      <c r="C6">
+        <v>464.2456400881699</v>
+      </c>
+      <c r="D6">
+        <v>389.45764008817</v>
+      </c>
+      <c r="E6">
+        <v>-14.988</v>
+      </c>
+      <c r="F6">
+        <v>19.312</v>
+      </c>
+      <c r="G6">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H6">
+        <v>448.5</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>38.6</v>
+      </c>
+      <c r="K6">
+        <v>22.7</v>
+      </c>
+      <c r="L6">
+        <v>15.9</v>
+      </c>
+      <c r="M6">
+        <v>0.8632464000000001</v>
+      </c>
+      <c r="N6">
+        <v>15.0367536</v>
+      </c>
+      <c r="O6">
+        <v>2.556248112</v>
+      </c>
+      <c r="P6">
+        <v>12.480505488</v>
+      </c>
+      <c r="Q6">
+        <v>35.180505488</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.0833089167123474</v>
+      </c>
+      <c r="T6">
+        <v>0.9675851459205956</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.17</v>
+      </c>
+      <c r="W6">
+        <v>0.037101</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>18.418843102039</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.08137047416782192</v>
+      </c>
+      <c r="C7">
+        <v>460.2421601734236</v>
+      </c>
+      <c r="D7">
+        <v>390.2821601734236</v>
+      </c>
+      <c r="E7">
+        <v>-10.16</v>
+      </c>
+      <c r="F7">
+        <v>24.14</v>
+      </c>
+      <c r="G7">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H7">
+        <v>448.5</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>38.6</v>
+      </c>
+      <c r="K7">
+        <v>22.7</v>
+      </c>
+      <c r="L7">
+        <v>15.9</v>
+      </c>
+      <c r="M7">
+        <v>1.079058</v>
+      </c>
+      <c r="N7">
+        <v>14.820942</v>
+      </c>
+      <c r="O7">
+        <v>2.51956014</v>
+      </c>
+      <c r="P7">
+        <v>12.30138186</v>
+      </c>
+      <c r="Q7">
+        <v>35.00138186</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.08370044649244414</v>
+      </c>
+      <c r="T7">
+        <v>0.9760966628792204</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.17</v>
+      </c>
+      <c r="W7">
+        <v>0.037101</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>14.7350744816312</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.08133512829179038</v>
+      </c>
+      <c r="C8">
+        <v>455.7384771651624</v>
+      </c>
+      <c r="D8">
+        <v>390.6064771651624</v>
+      </c>
+      <c r="E8">
+        <v>-5.331999999999997</v>
+      </c>
+      <c r="F8">
+        <v>28.968</v>
+      </c>
+      <c r="G8">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H8">
+        <v>448.5</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>38.6</v>
+      </c>
+      <c r="K8">
+        <v>22.7</v>
+      </c>
+      <c r="L8">
+        <v>15.9</v>
+      </c>
+      <c r="M8">
+        <v>1.3267344</v>
+      </c>
+      <c r="N8">
+        <v>14.5732656</v>
+      </c>
+      <c r="O8">
+        <v>2.477455152</v>
+      </c>
+      <c r="P8">
+        <v>12.095810448</v>
+      </c>
+      <c r="Q8">
+        <v>34.795810448</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.08410030669339401</v>
+      </c>
+      <c r="T8">
+        <v>0.984789275943348</v>
+      </c>
+      <c r="U8">
+        <v>0.0458</v>
+      </c>
+      <c r="V8">
+        <v>0.17</v>
+      </c>
+      <c r="W8">
+        <v>0.038014</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>11.98431276071533</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.0812541324157588</v>
+      </c>
+      <c r="C9">
+        <v>451.6556935198807</v>
+      </c>
+      <c r="D9">
+        <v>391.3516935198807</v>
+      </c>
+      <c r="E9">
+        <v>-0.5039999999999907</v>
+      </c>
+      <c r="F9">
+        <v>33.79600000000001</v>
+      </c>
+      <c r="G9">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H9">
+        <v>448.5</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>38.6</v>
+      </c>
+      <c r="K9">
+        <v>22.7</v>
+      </c>
+      <c r="L9">
+        <v>15.9</v>
+      </c>
+      <c r="M9">
+        <v>1.5478568</v>
+      </c>
+      <c r="N9">
+        <v>14.3521432</v>
+      </c>
+      <c r="O9">
+        <v>2.439864344</v>
+      </c>
+      <c r="P9">
+        <v>11.912278856</v>
+      </c>
+      <c r="Q9">
+        <v>34.612278856</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.08450876603845033</v>
+      </c>
+      <c r="T9">
+        <v>0.9936688269228332</v>
+      </c>
+      <c r="U9">
+        <v>0.0458</v>
+      </c>
+      <c r="V9">
+        <v>0.17</v>
+      </c>
+      <c r="W9">
+        <v>0.038014</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>10.27226808061314</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.08131921653972723</v>
+      </c>
+      <c r="C10">
+        <v>446.2286518580356</v>
+      </c>
+      <c r="D10">
+        <v>390.7526518580357</v>
+      </c>
+      <c r="E10">
+        <v>4.324000000000005</v>
+      </c>
+      <c r="F10">
+        <v>38.624</v>
+      </c>
+      <c r="G10">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H10">
+        <v>448.5</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>38.6</v>
+      </c>
+      <c r="K10">
+        <v>22.7</v>
+      </c>
+      <c r="L10">
+        <v>15.9</v>
+      </c>
+      <c r="M10">
+        <v>1.853952</v>
+      </c>
+      <c r="N10">
+        <v>14.046048</v>
+      </c>
+      <c r="O10">
+        <v>2.38782816</v>
+      </c>
+      <c r="P10">
+        <v>11.65821984</v>
+      </c>
+      <c r="Q10">
+        <v>34.35821984</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.08492610493448612</v>
+      </c>
+      <c r="T10">
+        <v>1.002741411619263</v>
+      </c>
+      <c r="U10">
+        <v>0.048</v>
+      </c>
+      <c r="V10">
+        <v>0.17</v>
+      </c>
+      <c r="W10">
+        <v>0.03984</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>8.576273819386909</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.08136853066369566</v>
+      </c>
+      <c r="C11">
+        <v>440.9479788525482</v>
+      </c>
+      <c r="D11">
+        <v>390.2999788525482</v>
+      </c>
+      <c r="E11">
+        <v>9.152000000000001</v>
+      </c>
+      <c r="F11">
+        <v>43.452</v>
+      </c>
+      <c r="G11">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H11">
+        <v>448.5</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>38.6</v>
+      </c>
+      <c r="K11">
+        <v>22.7</v>
+      </c>
+      <c r="L11">
+        <v>15.9</v>
+      </c>
+      <c r="M11">
+        <v>2.150874</v>
+      </c>
+      <c r="N11">
+        <v>13.749126</v>
+      </c>
+      <c r="O11">
+        <v>2.33735142</v>
+      </c>
+      <c r="P11">
+        <v>11.41177458</v>
+      </c>
+      <c r="Q11">
+        <v>34.11177458</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.08535261611395129</v>
+      </c>
+      <c r="T11">
+        <v>1.01201339378155</v>
+      </c>
+      <c r="U11">
+        <v>0.0495</v>
+      </c>
+      <c r="V11">
+        <v>0.17</v>
+      </c>
+      <c r="W11">
+        <v>0.041085</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>7.392343763511948</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.08131824478766411</v>
+      </c>
+      <c r="C12">
+        <v>436.5815824876398</v>
+      </c>
+      <c r="D12">
+        <v>390.7615824876398</v>
+      </c>
+      <c r="E12">
+        <v>13.98</v>
+      </c>
+      <c r="F12">
+        <v>48.28</v>
+      </c>
+      <c r="G12">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H12">
+        <v>448.5</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>38.6</v>
+      </c>
+      <c r="K12">
+        <v>22.7</v>
+      </c>
+      <c r="L12">
+        <v>15.9</v>
+      </c>
+      <c r="M12">
+        <v>2.38986</v>
+      </c>
+      <c r="N12">
+        <v>13.51014</v>
+      </c>
+      <c r="O12">
+        <v>2.2967238</v>
+      </c>
+      <c r="P12">
+        <v>11.2134162</v>
+      </c>
+      <c r="Q12">
+        <v>33.9134162</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.08578860531962679</v>
+      </c>
+      <c r="T12">
+        <v>1.021491419991887</v>
+      </c>
+      <c r="U12">
+        <v>0.0495</v>
+      </c>
+      <c r="V12">
+        <v>0.17</v>
+      </c>
+      <c r="W12">
+        <v>0.041085</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>6.653109387160753</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.08139577891163254</v>
+      </c>
+      <c r="C13">
+        <v>431.0423064468483</v>
+      </c>
+      <c r="D13">
+        <v>390.0503064468483</v>
+      </c>
+      <c r="E13">
+        <v>18.80800000000001</v>
+      </c>
+      <c r="F13">
+        <v>53.108</v>
+      </c>
+      <c r="G13">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H13">
+        <v>448.5</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>38.6</v>
+      </c>
+      <c r="K13">
+        <v>22.7</v>
+      </c>
+      <c r="L13">
+        <v>15.9</v>
+      </c>
+      <c r="M13">
+        <v>2.7031972</v>
+      </c>
+      <c r="N13">
+        <v>13.1968028</v>
+      </c>
+      <c r="O13">
+        <v>2.243456476</v>
+      </c>
+      <c r="P13">
+        <v>10.953346324</v>
+      </c>
+      <c r="Q13">
+        <v>33.653346324</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.08623439203554217</v>
+      </c>
+      <c r="T13">
+        <v>1.031182435555265</v>
+      </c>
+      <c r="U13">
+        <v>0.0509</v>
+      </c>
+      <c r="V13">
+        <v>0.17</v>
+      </c>
+      <c r="W13">
+        <v>0.042247</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>5.881923819690253</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.08135711303560098</v>
+      </c>
+      <c r="C14">
+        <v>426.5686922526366</v>
+      </c>
+      <c r="D14">
+        <v>390.4046922526366</v>
+      </c>
+      <c r="E14">
+        <v>23.636</v>
+      </c>
+      <c r="F14">
+        <v>57.936</v>
+      </c>
+      <c r="G14">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H14">
+        <v>448.5</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>38.6</v>
+      </c>
+      <c r="K14">
+        <v>22.7</v>
+      </c>
+      <c r="L14">
+        <v>15.9</v>
+      </c>
+      <c r="M14">
+        <v>2.9489424</v>
+      </c>
+      <c r="N14">
+        <v>12.9510576</v>
+      </c>
+      <c r="O14">
+        <v>2.201679792</v>
+      </c>
+      <c r="P14">
+        <v>10.749377808</v>
+      </c>
+      <c r="Q14">
+        <v>33.449377808</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.08669031026772839</v>
+      </c>
+      <c r="T14">
+        <v>1.041093701472356</v>
+      </c>
+      <c r="U14">
+        <v>0.0509</v>
+      </c>
+      <c r="V14">
+        <v>0.17</v>
+      </c>
+      <c r="W14">
+        <v>0.042247</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>5.391763501382733</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.08131844715956942</v>
+      </c>
+      <c r="C15">
+        <v>422.0957226086637</v>
+      </c>
+      <c r="D15">
+        <v>390.7597226086637</v>
+      </c>
+      <c r="E15">
+        <v>28.46400000000001</v>
+      </c>
+      <c r="F15">
+        <v>62.764</v>
+      </c>
+      <c r="G15">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H15">
+        <v>448.5</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>38.6</v>
+      </c>
+      <c r="K15">
+        <v>22.7</v>
+      </c>
+      <c r="L15">
+        <v>15.9</v>
+      </c>
+      <c r="M15">
+        <v>3.1946876</v>
+      </c>
+      <c r="N15">
+        <v>12.7053124</v>
+      </c>
+      <c r="O15">
+        <v>2.159903108</v>
+      </c>
+      <c r="P15">
+        <v>10.545409292</v>
+      </c>
+      <c r="Q15">
+        <v>33.24540929200001</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.08715670937881542</v>
+      </c>
+      <c r="T15">
+        <v>1.051232812582944</v>
+      </c>
+      <c r="U15">
+        <v>0.0509</v>
+      </c>
+      <c r="V15">
+        <v>0.17</v>
+      </c>
+      <c r="W15">
+        <v>0.042247</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>4.977012462814829</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.08127978128353786</v>
+      </c>
+      <c r="C16">
+        <v>417.6233992749738</v>
+      </c>
+      <c r="D16">
+        <v>391.1153992749739</v>
+      </c>
+      <c r="E16">
+        <v>33.29200000000002</v>
+      </c>
+      <c r="F16">
+        <v>67.59200000000001</v>
+      </c>
+      <c r="G16">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H16">
+        <v>448.5</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>38.6</v>
+      </c>
+      <c r="K16">
+        <v>22.7</v>
+      </c>
+      <c r="L16">
+        <v>15.9</v>
+      </c>
+      <c r="M16">
+        <v>3.440432800000001</v>
+      </c>
+      <c r="N16">
+        <v>12.4595672</v>
+      </c>
+      <c r="O16">
+        <v>2.118126424</v>
+      </c>
+      <c r="P16">
+        <v>10.341440776</v>
+      </c>
+      <c r="Q16">
+        <v>33.041440776</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.08763395498085796</v>
+      </c>
+      <c r="T16">
+        <v>1.061607716975173</v>
+      </c>
+      <c r="U16">
+        <v>0.0509</v>
+      </c>
+      <c r="V16">
+        <v>0.17</v>
+      </c>
+      <c r="W16">
+        <v>0.042247</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>4.62151157261377</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.08156481540750626</v>
+      </c>
+      <c r="C17">
+        <v>410.1885545092338</v>
+      </c>
+      <c r="D17">
+        <v>388.5085545092338</v>
+      </c>
+      <c r="E17">
+        <v>38.12</v>
+      </c>
+      <c r="F17">
+        <v>72.42</v>
+      </c>
+      <c r="G17">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H17">
+        <v>448.5</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>38.6</v>
+      </c>
+      <c r="K17">
+        <v>22.7</v>
+      </c>
+      <c r="L17">
+        <v>15.9</v>
+      </c>
+      <c r="M17">
+        <v>3.87447</v>
+      </c>
+      <c r="N17">
+        <v>12.02553</v>
+      </c>
+      <c r="O17">
+        <v>2.0443401</v>
+      </c>
+      <c r="P17">
+        <v>9.981189899999999</v>
+      </c>
+      <c r="Q17">
+        <v>32.6811899</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.08812242989118385</v>
+      </c>
+      <c r="T17">
+        <v>1.072226736764866</v>
+      </c>
+      <c r="U17">
+        <v>0.0535</v>
+      </c>
+      <c r="V17">
+        <v>0.17</v>
+      </c>
+      <c r="W17">
+        <v>0.044405</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>4.10378709862252</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.08190628953147472</v>
+      </c>
+      <c r="C18">
+        <v>402.2829150337131</v>
+      </c>
+      <c r="D18">
+        <v>385.4309150337131</v>
+      </c>
+      <c r="E18">
+        <v>42.94800000000001</v>
+      </c>
+      <c r="F18">
+        <v>77.248</v>
+      </c>
+      <c r="G18">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H18">
+        <v>448.5</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>38.6</v>
+      </c>
+      <c r="K18">
+        <v>22.7</v>
+      </c>
+      <c r="L18">
+        <v>15.9</v>
+      </c>
+      <c r="M18">
+        <v>4.3413376</v>
+      </c>
+      <c r="N18">
+        <v>11.5586624</v>
+      </c>
+      <c r="O18">
+        <v>1.964972608</v>
+      </c>
+      <c r="P18">
+        <v>9.593689791999999</v>
+      </c>
+      <c r="Q18">
+        <v>32.293689792</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.08862253515651752</v>
+      </c>
+      <c r="T18">
+        <v>1.083098590359076</v>
+      </c>
+      <c r="U18">
+        <v>0.0562</v>
+      </c>
+      <c r="V18">
+        <v>0.17</v>
+      </c>
+      <c r="W18">
+        <v>0.046646</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>3.66246568799441</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.08257478365544313</v>
+      </c>
+      <c r="C19">
+        <v>391.568916740178</v>
+      </c>
+      <c r="D19">
+        <v>379.5449167401781</v>
+      </c>
+      <c r="E19">
+        <v>47.77600000000001</v>
+      </c>
+      <c r="F19">
+        <v>82.07600000000001</v>
+      </c>
+      <c r="G19">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H19">
+        <v>448.5</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>38.6</v>
+      </c>
+      <c r="K19">
+        <v>22.7</v>
+      </c>
+      <c r="L19">
+        <v>15.9</v>
+      </c>
+      <c r="M19">
+        <v>4.998428400000001</v>
+      </c>
+      <c r="N19">
+        <v>10.9015716</v>
+      </c>
+      <c r="O19">
+        <v>1.853267172</v>
+      </c>
+      <c r="P19">
+        <v>9.048304427999998</v>
+      </c>
+      <c r="Q19">
+        <v>31.748304428</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.08913469115113631</v>
+      </c>
+      <c r="T19">
+        <v>1.09423241632905</v>
+      </c>
+      <c r="U19">
+        <v>0.0609</v>
+      </c>
+      <c r="V19">
+        <v>0.17</v>
+      </c>
+      <c r="W19">
+        <v>0.050547</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>3.18099985187344</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.0826191177794116</v>
+      </c>
+      <c r="C20">
+        <v>386.3569110311844</v>
+      </c>
+      <c r="D20">
+        <v>379.1609110311844</v>
+      </c>
+      <c r="E20">
+        <v>52.604</v>
+      </c>
+      <c r="F20">
+        <v>86.904</v>
+      </c>
+      <c r="G20">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H20">
+        <v>448.5</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>38.6</v>
+      </c>
+      <c r="K20">
+        <v>22.7</v>
+      </c>
+      <c r="L20">
+        <v>15.9</v>
+      </c>
+      <c r="M20">
+        <v>5.2924536</v>
+      </c>
+      <c r="N20">
+        <v>10.6075464</v>
+      </c>
+      <c r="O20">
+        <v>1.803282888</v>
+      </c>
+      <c r="P20">
+        <v>8.804263511999999</v>
+      </c>
+      <c r="Q20">
+        <v>31.504263512</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.08965933875537999</v>
+      </c>
+      <c r="T20">
+        <v>1.105637799029999</v>
+      </c>
+      <c r="U20">
+        <v>0.0609</v>
+      </c>
+      <c r="V20">
+        <v>0.17</v>
+      </c>
+      <c r="W20">
+        <v>0.050547</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>3.004277637880472</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.08487125190338002</v>
+      </c>
+      <c r="C21">
+        <v>362.9941156668406</v>
+      </c>
+      <c r="D21">
+        <v>360.6261156668405</v>
+      </c>
+      <c r="E21">
+        <v>57.432</v>
+      </c>
+      <c r="F21">
+        <v>91.732</v>
+      </c>
+      <c r="G21">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H21">
+        <v>448.5</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>38.6</v>
+      </c>
+      <c r="K21">
+        <v>22.7</v>
+      </c>
+      <c r="L21">
+        <v>15.9</v>
+      </c>
+      <c r="M21">
+        <v>6.870726799999999</v>
+      </c>
+      <c r="N21">
+        <v>9.029273199999999</v>
+      </c>
+      <c r="O21">
+        <v>1.534976444</v>
+      </c>
+      <c r="P21">
+        <v>7.494296755999999</v>
+      </c>
+      <c r="Q21">
+        <v>30.194296756</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.09019694062145681</v>
+      </c>
+      <c r="T21">
+        <v>1.117324796118626</v>
+      </c>
+      <c r="U21">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V21">
+        <v>0.17</v>
+      </c>
+      <c r="W21">
+        <v>0.06216699999999999</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>2.314165657117963</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.08503178602734845</v>
+      </c>
+      <c r="C22">
+        <v>356.9138863559403</v>
+      </c>
+      <c r="D22">
+        <v>359.3738863559403</v>
+      </c>
+      <c r="E22">
+        <v>62.26000000000001</v>
+      </c>
+      <c r="F22">
+        <v>96.56</v>
+      </c>
+      <c r="G22">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H22">
+        <v>448.5</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>38.6</v>
+      </c>
+      <c r="K22">
+        <v>22.7</v>
+      </c>
+      <c r="L22">
+        <v>15.9</v>
+      </c>
+      <c r="M22">
+        <v>7.232343999999999</v>
+      </c>
+      <c r="N22">
+        <v>8.667655999999999</v>
+      </c>
+      <c r="O22">
+        <v>1.47350152</v>
+      </c>
+      <c r="P22">
+        <v>7.194154479999999</v>
+      </c>
+      <c r="Q22">
+        <v>29.89415448</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.09074798253418556</v>
+      </c>
+      <c r="T22">
+        <v>1.129303968134469</v>
+      </c>
+      <c r="U22">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V22">
+        <v>0.17</v>
+      </c>
+      <c r="W22">
+        <v>0.06216699999999999</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>2.198457374262065</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.08519232015131689</v>
+      </c>
+      <c r="C23">
+        <v>350.842323373207</v>
+      </c>
+      <c r="D23">
+        <v>358.1303233732071</v>
+      </c>
+      <c r="E23">
+        <v>67.08800000000001</v>
+      </c>
+      <c r="F23">
+        <v>101.388</v>
+      </c>
+      <c r="G23">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H23">
+        <v>448.5</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>38.6</v>
+      </c>
+      <c r="K23">
+        <v>22.7</v>
+      </c>
+      <c r="L23">
+        <v>15.9</v>
+      </c>
+      <c r="M23">
+        <v>7.5939612</v>
+      </c>
+      <c r="N23">
+        <v>8.3060388</v>
+      </c>
+      <c r="O23">
+        <v>1.412026596</v>
+      </c>
+      <c r="P23">
+        <v>6.894012203999999</v>
+      </c>
+      <c r="Q23">
+        <v>29.594012204</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.09131297487508466</v>
+      </c>
+      <c r="T23">
+        <v>1.141586410327927</v>
+      </c>
+      <c r="U23">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V23">
+        <v>0.17</v>
+      </c>
+      <c r="W23">
+        <v>0.06216699999999999</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>2.093768927868633</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.08832923427528533</v>
+      </c>
+      <c r="C24">
+        <v>323.3322834416635</v>
+      </c>
+      <c r="D24">
+        <v>335.4482834416635</v>
+      </c>
+      <c r="E24">
+        <v>71.91600000000001</v>
+      </c>
+      <c r="F24">
+        <v>106.216</v>
+      </c>
+      <c r="G24">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H24">
+        <v>448.5</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>38.6</v>
+      </c>
+      <c r="K24">
+        <v>22.7</v>
+      </c>
+      <c r="L24">
+        <v>15.9</v>
+      </c>
+      <c r="M24">
+        <v>9.686899200000001</v>
+      </c>
+      <c r="N24">
+        <v>6.213100799999998</v>
+      </c>
+      <c r="O24">
+        <v>1.056227136</v>
+      </c>
+      <c r="P24">
+        <v>5.156873663999998</v>
+      </c>
+      <c r="Q24">
+        <v>27.856873664</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.09189245419908373</v>
+      </c>
+      <c r="T24">
+        <v>1.154183786936603</v>
+      </c>
+      <c r="U24">
+        <v>0.0912</v>
+      </c>
+      <c r="V24">
+        <v>0.17</v>
+      </c>
+      <c r="W24">
+        <v>0.075696</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>1.641392118542949</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.08862505839925375</v>
+      </c>
+      <c r="C25">
+        <v>316.5126411280576</v>
+      </c>
+      <c r="D25">
+        <v>333.4566411280576</v>
+      </c>
+      <c r="E25">
+        <v>76.74400000000001</v>
+      </c>
+      <c r="F25">
+        <v>111.044</v>
+      </c>
+      <c r="G25">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H25">
+        <v>448.5</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>38.6</v>
+      </c>
+      <c r="K25">
+        <v>22.7</v>
+      </c>
+      <c r="L25">
+        <v>15.9</v>
+      </c>
+      <c r="M25">
+        <v>10.1272128</v>
+      </c>
+      <c r="N25">
+        <v>5.772787199999998</v>
+      </c>
+      <c r="O25">
+        <v>0.9813738239999997</v>
+      </c>
+      <c r="P25">
+        <v>4.791413375999999</v>
+      </c>
+      <c r="Q25">
+        <v>27.491413376</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.09248698493409578</v>
+      </c>
+      <c r="T25">
+        <v>1.167108368132517</v>
+      </c>
+      <c r="U25">
+        <v>0.0912</v>
+      </c>
+      <c r="V25">
+        <v>0.17</v>
+      </c>
+      <c r="W25">
+        <v>0.075696</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>1.57002724382369</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.08892088252322217</v>
+      </c>
+      <c r="C26">
+        <v>309.7165090087267</v>
+      </c>
+      <c r="D26">
+        <v>331.4885090087268</v>
+      </c>
+      <c r="E26">
+        <v>81.572</v>
+      </c>
+      <c r="F26">
+        <v>115.872</v>
+      </c>
+      <c r="G26">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H26">
+        <v>448.5</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>38.6</v>
+      </c>
+      <c r="K26">
+        <v>22.7</v>
+      </c>
+      <c r="L26">
+        <v>15.9</v>
+      </c>
+      <c r="M26">
+        <v>10.5675264</v>
+      </c>
+      <c r="N26">
+        <v>5.332473599999998</v>
+      </c>
+      <c r="O26">
+        <v>0.9065205119999998</v>
+      </c>
+      <c r="P26">
+        <v>4.425953087999998</v>
+      </c>
+      <c r="Q26">
+        <v>27.125953088</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.09309716121476602</v>
+      </c>
+      <c r="T26">
+        <v>1.180373069886218</v>
+      </c>
+      <c r="U26">
+        <v>0.0912</v>
+      </c>
+      <c r="V26">
+        <v>0.17</v>
+      </c>
+      <c r="W26">
+        <v>0.075696</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>1.504609441997703</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.104134468660465</v>
+      </c>
+      <c r="C27">
+        <v>227.6991005891228</v>
+      </c>
+      <c r="D27">
+        <v>254.2991005891228</v>
+      </c>
+      <c r="E27">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="F27">
+        <v>120.7</v>
+      </c>
+      <c r="G27">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H27">
+        <v>448.5</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>38.6</v>
+      </c>
+      <c r="K27">
+        <v>22.7</v>
+      </c>
+      <c r="L27">
+        <v>15.9</v>
+      </c>
+      <c r="M27">
+        <v>18.90162</v>
+      </c>
+      <c r="N27">
+        <v>-3.001620000000003</v>
+      </c>
+      <c r="O27">
+        <v>-0.5102754000000005</v>
+      </c>
+      <c r="P27">
+        <v>-2.491344600000002</v>
+      </c>
+      <c r="Q27">
+        <v>20.2086554</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.09411074694634766</v>
+      </c>
+      <c r="T27">
+        <v>1.202407542311906</v>
+      </c>
+      <c r="U27">
+        <v>0.1566</v>
+      </c>
+      <c r="V27">
+        <v>0.1430036155631104</v>
+      </c>
+      <c r="W27">
+        <v>0.1342056338028169</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>0.841197738606532</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.105312468660465</v>
+      </c>
+      <c r="C28">
+        <v>218.367218136297</v>
+      </c>
+      <c r="D28">
+        <v>249.795218136297</v>
+      </c>
+      <c r="E28">
+        <v>91.22800000000001</v>
+      </c>
+      <c r="F28">
+        <v>125.528</v>
+      </c>
+      <c r="G28">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H28">
+        <v>448.5</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>38.6</v>
+      </c>
+      <c r="K28">
+        <v>22.7</v>
+      </c>
+      <c r="L28">
+        <v>15.9</v>
+      </c>
+      <c r="M28">
+        <v>19.6576848</v>
+      </c>
+      <c r="N28">
+        <v>-3.757684800000003</v>
+      </c>
+      <c r="O28">
+        <v>-0.6388064160000007</v>
+      </c>
+      <c r="P28">
+        <v>-3.118878384000003</v>
+      </c>
+      <c r="Q28">
+        <v>19.581121616</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.09485818947264965</v>
+      </c>
+      <c r="T28">
+        <v>1.218656292883688</v>
+      </c>
+      <c r="U28">
+        <v>0.1566</v>
+      </c>
+      <c r="V28">
+        <v>0.1375034765029908</v>
+      </c>
+      <c r="W28">
+        <v>0.1350669555796317</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.8088439794293577</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1209689794950197</v>
+      </c>
+      <c r="C29">
+        <v>165.9431354880034</v>
+      </c>
+      <c r="D29">
+        <v>202.1991354880035</v>
+      </c>
+      <c r="E29">
+        <v>96.05600000000003</v>
+      </c>
+      <c r="F29">
+        <v>130.356</v>
+      </c>
+      <c r="G29">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H29">
+        <v>448.5</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>38.6</v>
+      </c>
+      <c r="K29">
+        <v>22.7</v>
+      </c>
+      <c r="L29">
+        <v>15.9</v>
+      </c>
+      <c r="M29">
+        <v>27.21833280000001</v>
+      </c>
+      <c r="N29">
+        <v>-11.31833280000001</v>
+      </c>
+      <c r="O29">
+        <v>-1.924116576000001</v>
+      </c>
+      <c r="P29">
+        <v>-9.394216224000006</v>
+      </c>
+      <c r="Q29">
+        <v>13.305783776</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.09615283704700753</v>
+      </c>
+      <c r="T29">
+        <v>1.246800805369729</v>
+      </c>
+      <c r="U29">
+        <v>0.2088</v>
+      </c>
+      <c r="V29">
+        <v>0.09930806636327114</v>
+      </c>
+      <c r="W29">
+        <v>0.188064475743349</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.5841650962545361</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1226689794950197</v>
+      </c>
+      <c r="C30">
+        <v>157.0166173899024</v>
+      </c>
+      <c r="D30">
+        <v>198.1006173899024</v>
+      </c>
+      <c r="E30">
+        <v>100.884</v>
+      </c>
+      <c r="F30">
+        <v>135.184</v>
+      </c>
+      <c r="G30">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H30">
+        <v>448.5</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>38.6</v>
+      </c>
+      <c r="K30">
+        <v>22.7</v>
+      </c>
+      <c r="L30">
+        <v>15.9</v>
+      </c>
+      <c r="M30">
+        <v>28.22641920000001</v>
+      </c>
+      <c r="N30">
+        <v>-12.32641920000001</v>
+      </c>
+      <c r="O30">
+        <v>-2.095491264000001</v>
+      </c>
+      <c r="P30">
+        <v>-10.23092793600001</v>
+      </c>
+      <c r="Q30">
+        <v>12.469072064</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.09694940422821596</v>
+      </c>
+      <c r="T30">
+        <v>1.264117483222086</v>
+      </c>
+      <c r="U30">
+        <v>0.2088</v>
+      </c>
+      <c r="V30">
+        <v>0.09576134970744002</v>
+      </c>
+      <c r="W30">
+        <v>0.1888050301810865</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.5633020571025883</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1243689794950197</v>
+      </c>
+      <c r="C31">
+        <v>148.2529499137881</v>
+      </c>
+      <c r="D31">
+        <v>194.1649499137881</v>
+      </c>
+      <c r="E31">
+        <v>105.712</v>
+      </c>
+      <c r="F31">
+        <v>140.012</v>
+      </c>
+      <c r="G31">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H31">
+        <v>448.5</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>38.6</v>
+      </c>
+      <c r="K31">
+        <v>22.7</v>
+      </c>
+      <c r="L31">
+        <v>15.9</v>
+      </c>
+      <c r="M31">
+        <v>29.2345056</v>
+      </c>
+      <c r="N31">
+        <v>-13.3345056</v>
+      </c>
+      <c r="O31">
+        <v>-2.266865952000001</v>
+      </c>
+      <c r="P31">
+        <v>-11.067639648</v>
+      </c>
+      <c r="Q31">
+        <v>11.632360352</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.09776840992157113</v>
+      </c>
+      <c r="T31">
+        <v>1.281921954816764</v>
+      </c>
+      <c r="U31">
+        <v>0.2088</v>
+      </c>
+      <c r="V31">
+        <v>0.09245923420028694</v>
+      </c>
+      <c r="W31">
+        <v>0.1894945118989801</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.5438778482369819</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1260689794950197</v>
+      </c>
+      <c r="C32">
+        <v>139.6426160677475</v>
+      </c>
+      <c r="D32">
+        <v>190.3826160677475</v>
+      </c>
+      <c r="E32">
+        <v>110.54</v>
+      </c>
+      <c r="F32">
+        <v>144.84</v>
+      </c>
+      <c r="G32">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H32">
+        <v>448.5</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>38.6</v>
+      </c>
+      <c r="K32">
+        <v>22.7</v>
+      </c>
+      <c r="L32">
+        <v>15.9</v>
+      </c>
+      <c r="M32">
+        <v>30.242592</v>
+      </c>
+      <c r="N32">
+        <v>-14.342592</v>
+      </c>
+      <c r="O32">
+        <v>-2.438240640000001</v>
+      </c>
+      <c r="P32">
+        <v>-11.90435136</v>
+      </c>
+      <c r="Q32">
+        <v>10.79564864</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.09861081577759358</v>
+      </c>
+      <c r="T32">
+        <v>1.30023512559986</v>
+      </c>
+      <c r="U32">
+        <v>0.2088</v>
+      </c>
+      <c r="V32">
+        <v>0.08937725972694403</v>
+      </c>
+      <c r="W32">
+        <v>0.1901380281690141</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.5257485866290825</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1277689794950197</v>
+      </c>
+      <c r="C33">
+        <v>131.176826254352</v>
+      </c>
+      <c r="D33">
+        <v>186.744826254352</v>
+      </c>
+      <c r="E33">
+        <v>115.368</v>
+      </c>
+      <c r="F33">
+        <v>149.668</v>
+      </c>
+      <c r="G33">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H33">
+        <v>448.5</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>38.6</v>
+      </c>
+      <c r="K33">
+        <v>22.7</v>
+      </c>
+      <c r="L33">
+        <v>15.9</v>
+      </c>
+      <c r="M33">
+        <v>31.2506784</v>
+      </c>
+      <c r="N33">
+        <v>-15.3506784</v>
+      </c>
+      <c r="O33">
+        <v>-2.609615328000001</v>
+      </c>
+      <c r="P33">
+        <v>-12.741063072</v>
+      </c>
+      <c r="Q33">
+        <v>9.958936928</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.09947763919466014</v>
+      </c>
+      <c r="T33">
+        <v>1.319079112927394</v>
+      </c>
+      <c r="U33">
+        <v>0.2088</v>
+      </c>
+      <c r="V33">
+        <v>0.08649412231639744</v>
+      </c>
+      <c r="W33">
+        <v>0.1907400272603362</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.5087889548023379</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1392138956386962</v>
+      </c>
+      <c r="C34">
+        <v>105.0641339002508</v>
+      </c>
+      <c r="D34">
+        <v>165.4601339002508</v>
+      </c>
+      <c r="E34">
+        <v>120.196</v>
+      </c>
+      <c r="F34">
+        <v>154.496</v>
+      </c>
+      <c r="G34">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H34">
+        <v>448.5</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>38.6</v>
+      </c>
+      <c r="K34">
+        <v>22.7</v>
+      </c>
+      <c r="L34">
+        <v>15.9</v>
+      </c>
+      <c r="M34">
+        <v>36.8936448</v>
+      </c>
+      <c r="N34">
+        <v>-20.99364480000001</v>
+      </c>
+      <c r="O34">
+        <v>-3.568919616000001</v>
+      </c>
+      <c r="P34">
+        <v>-17.424725184</v>
+      </c>
+      <c r="Q34">
+        <v>5.275274816</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1005830693941058</v>
+      </c>
+      <c r="T34">
+        <v>1.343110204219691</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>0.07326465071838063</v>
+      </c>
+      <c r="W34">
+        <v>0.2213044014084507</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.4309685336375331</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1412138956386961</v>
+      </c>
+      <c r="C35">
+        <v>97.00492913319505</v>
+      </c>
+      <c r="D35">
+        <v>162.2289291331951</v>
+      </c>
+      <c r="E35">
+        <v>125.024</v>
+      </c>
+      <c r="F35">
+        <v>159.324</v>
+      </c>
+      <c r="G35">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H35">
+        <v>448.5</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>38.6</v>
+      </c>
+      <c r="K35">
+        <v>22.7</v>
+      </c>
+      <c r="L35">
+        <v>15.9</v>
+      </c>
+      <c r="M35">
+        <v>38.0465712</v>
+      </c>
+      <c r="N35">
+        <v>-22.1465712</v>
+      </c>
+      <c r="O35">
+        <v>-3.764917104000001</v>
+      </c>
+      <c r="P35">
+        <v>-18.381654096</v>
+      </c>
+      <c r="Q35">
+        <v>4.318345904000001</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1015052047581969</v>
+      </c>
+      <c r="T35">
+        <v>1.363156625178193</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>0.07104450978752061</v>
+      </c>
+      <c r="W35">
+        <v>0.2218345710627401</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.4179088811030623</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1432138956386961</v>
+      </c>
+      <c r="C36">
+        <v>89.06950883935684</v>
+      </c>
+      <c r="D36">
+        <v>159.1215088393569</v>
+      </c>
+      <c r="E36">
+        <v>129.852</v>
+      </c>
+      <c r="F36">
+        <v>164.152</v>
+      </c>
+      <c r="G36">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H36">
+        <v>448.5</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>38.6</v>
+      </c>
+      <c r="K36">
+        <v>22.7</v>
+      </c>
+      <c r="L36">
+        <v>15.9</v>
+      </c>
+      <c r="M36">
+        <v>39.19949760000001</v>
+      </c>
+      <c r="N36">
+        <v>-23.29949760000001</v>
+      </c>
+      <c r="O36">
+        <v>-3.960914592000002</v>
+      </c>
+      <c r="P36">
+        <v>-19.33858300800001</v>
+      </c>
+      <c r="Q36">
+        <v>3.361416991999995</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1024552836181696</v>
+      </c>
+      <c r="T36">
+        <v>1.383810513438469</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>0.06895496538200528</v>
+      </c>
+      <c r="W36">
+        <v>0.2223335542667771</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.4056174434235605</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1452138956386962</v>
+      </c>
+      <c r="C37">
+        <v>81.2508936027975</v>
+      </c>
+      <c r="D37">
+        <v>156.1308936027975</v>
+      </c>
+      <c r="E37">
+        <v>134.68</v>
+      </c>
+      <c r="F37">
+        <v>168.98</v>
+      </c>
+      <c r="G37">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H37">
+        <v>448.5</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>38.6</v>
+      </c>
+      <c r="K37">
+        <v>22.7</v>
+      </c>
+      <c r="L37">
+        <v>15.9</v>
+      </c>
+      <c r="M37">
+        <v>40.35242400000001</v>
+      </c>
+      <c r="N37">
+        <v>-24.45242400000001</v>
+      </c>
+      <c r="O37">
+        <v>-4.156912080000001</v>
+      </c>
+      <c r="P37">
+        <v>-20.29551192000001</v>
+      </c>
+      <c r="Q37">
+        <v>2.404488079999997</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1034345956738337</v>
+      </c>
+      <c r="T37">
+        <v>1.405099905952907</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>0.06698482351394799</v>
+      </c>
+      <c r="W37">
+        <v>0.2228040241448692</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.3940283736114588</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1472138956386961</v>
+      </c>
+      <c r="C38">
+        <v>73.54261902760612</v>
+      </c>
+      <c r="D38">
+        <v>153.2506190276061</v>
+      </c>
+      <c r="E38">
+        <v>139.508</v>
+      </c>
+      <c r="F38">
+        <v>173.808</v>
+      </c>
+      <c r="G38">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H38">
+        <v>448.5</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>38.6</v>
+      </c>
+      <c r="K38">
+        <v>22.7</v>
+      </c>
+      <c r="L38">
+        <v>15.9</v>
+      </c>
+      <c r="M38">
+        <v>41.5053504</v>
+      </c>
+      <c r="N38">
+        <v>-25.6053504</v>
+      </c>
+      <c r="O38">
+        <v>-4.352909568</v>
+      </c>
+      <c r="P38">
+        <v>-21.252440832</v>
+      </c>
+      <c r="Q38">
+        <v>1.447559168000005</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1044445112312374</v>
+      </c>
+      <c r="T38">
+        <v>1.427054591983421</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>0.0651241339718939</v>
+      </c>
+      <c r="W38">
+        <v>0.2232483568075118</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.3830831410111406</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1492138956386961</v>
+      </c>
+      <c r="C39">
+        <v>65.938689093405</v>
+      </c>
+      <c r="D39">
+        <v>150.474689093405</v>
+      </c>
+      <c r="E39">
+        <v>144.336</v>
+      </c>
+      <c r="F39">
+        <v>178.636</v>
+      </c>
+      <c r="G39">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H39">
+        <v>448.5</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>38.6</v>
+      </c>
+      <c r="K39">
+        <v>22.7</v>
+      </c>
+      <c r="L39">
+        <v>15.9</v>
+      </c>
+      <c r="M39">
+        <v>42.6582768</v>
+      </c>
+      <c r="N39">
+        <v>-26.7582768</v>
+      </c>
+      <c r="O39">
+        <v>-4.548907056000001</v>
+      </c>
+      <c r="P39">
+        <v>-22.209369744</v>
+      </c>
+      <c r="Q39">
+        <v>0.4906302559999993</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1054864875999872</v>
+      </c>
+      <c r="T39">
+        <v>1.449706252173634</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>0.06336402224292378</v>
+      </c>
+      <c r="W39">
+        <v>0.2236686714883898</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.372729542605434</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1512138956386961</v>
+      </c>
+      <c r="C40">
+        <v>58.43353449008018</v>
+      </c>
+      <c r="D40">
+        <v>147.7975344900802</v>
+      </c>
+      <c r="E40">
+        <v>149.164</v>
+      </c>
+      <c r="F40">
+        <v>183.464</v>
+      </c>
+      <c r="G40">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H40">
+        <v>448.5</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>38.6</v>
+      </c>
+      <c r="K40">
+        <v>22.7</v>
+      </c>
+      <c r="L40">
+        <v>15.9</v>
+      </c>
+      <c r="M40">
+        <v>43.8112032</v>
+      </c>
+      <c r="N40">
+        <v>-27.9112032</v>
+      </c>
+      <c r="O40">
+        <v>-4.744904544000001</v>
+      </c>
+      <c r="P40">
+        <v>-23.166298656</v>
+      </c>
+      <c r="Q40">
+        <v>-0.4662986559999993</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1065620761096644</v>
+      </c>
+      <c r="T40">
+        <v>1.47308861107966</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>0.06169654797337316</v>
+      </c>
+      <c r="W40">
+        <v>0.2240668643439585</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.3629208704316068</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1532138956386961</v>
+      </c>
+      <c r="C41">
+        <v>51.02197532246294</v>
+      </c>
+      <c r="D41">
+        <v>145.2139753224629</v>
+      </c>
+      <c r="E41">
+        <v>153.992</v>
+      </c>
+      <c r="F41">
+        <v>188.292</v>
+      </c>
+      <c r="G41">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H41">
+        <v>448.5</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>38.6</v>
+      </c>
+      <c r="K41">
+        <v>22.7</v>
+      </c>
+      <c r="L41">
+        <v>15.9</v>
+      </c>
+      <c r="M41">
+        <v>44.9641296</v>
+      </c>
+      <c r="N41">
+        <v>-29.0641296</v>
+      </c>
+      <c r="O41">
+        <v>-4.940902032</v>
+      </c>
+      <c r="P41">
+        <v>-24.123227568</v>
+      </c>
+      <c r="Q41">
+        <v>-1.423227567999998</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1076729298163802</v>
+      </c>
+      <c r="T41">
+        <v>1.497237604703917</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>0.06011458520482514</v>
+      </c>
+      <c r="W41">
+        <v>0.2244446370530878</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.3536152070872066</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1552138956386961</v>
+      </c>
+      <c r="C42">
+        <v>43.69918765943081</v>
+      </c>
+      <c r="D42">
+        <v>142.7191876594308</v>
+      </c>
+      <c r="E42">
+        <v>158.82</v>
+      </c>
+      <c r="F42">
+        <v>193.12</v>
+      </c>
+      <c r="G42">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H42">
+        <v>448.5</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>38.6</v>
+      </c>
+      <c r="K42">
+        <v>22.7</v>
+      </c>
+      <c r="L42">
+        <v>15.9</v>
+      </c>
+      <c r="M42">
+        <v>46.11705600000001</v>
+      </c>
+      <c r="N42">
+        <v>-30.21705600000001</v>
+      </c>
+      <c r="O42">
+        <v>-5.136899520000002</v>
+      </c>
+      <c r="P42">
+        <v>-25.08015648000001</v>
+      </c>
+      <c r="Q42">
+        <v>-2.380156480000004</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1088208119799865</v>
+      </c>
+      <c r="T42">
+        <v>1.522191564782316</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0.05861172057470451</v>
+      </c>
+      <c r="W42">
+        <v>0.2248035211267606</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.3447748269100265</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1572138956386961</v>
+      </c>
+      <c r="C43">
+        <v>36.460673472905</v>
+      </c>
+      <c r="D43">
+        <v>140.308673472905</v>
+      </c>
+      <c r="E43">
+        <v>163.648</v>
+      </c>
+      <c r="F43">
+        <v>197.948</v>
+      </c>
+      <c r="G43">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H43">
+        <v>448.5</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>38.6</v>
+      </c>
+      <c r="K43">
+        <v>22.7</v>
+      </c>
+      <c r="L43">
+        <v>15.9</v>
+      </c>
+      <c r="M43">
+        <v>47.2699824</v>
+      </c>
+      <c r="N43">
+        <v>-31.3699824</v>
+      </c>
+      <c r="O43">
+        <v>-5.332897008000002</v>
+      </c>
+      <c r="P43">
+        <v>-26.037085392</v>
+      </c>
+      <c r="Q43">
+        <v>-3.337085391999999</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1100076054033761</v>
+      </c>
+      <c r="T43">
+        <v>1.547991421812525</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0.05718216641434586</v>
+      </c>
+      <c r="W43">
+        <v>0.2251448986602542</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.3363656847902697</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1592138956386961</v>
+      </c>
+      <c r="C44">
+        <v>29.30223357261471</v>
+      </c>
+      <c r="D44">
+        <v>137.9782335726147</v>
+      </c>
+      <c r="E44">
+        <v>168.476</v>
+      </c>
+      <c r="F44">
+        <v>202.776</v>
+      </c>
+      <c r="G44">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H44">
+        <v>448.5</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>38.6</v>
+      </c>
+      <c r="K44">
+        <v>22.7</v>
+      </c>
+      <c r="L44">
+        <v>15.9</v>
+      </c>
+      <c r="M44">
+        <v>48.4229088</v>
+      </c>
+      <c r="N44">
+        <v>-32.5229088</v>
+      </c>
+      <c r="O44">
+        <v>-5.528894496000001</v>
+      </c>
+      <c r="P44">
+        <v>-26.994014304</v>
+      </c>
+      <c r="Q44">
+        <v>-4.294014304000001</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1112353227379171</v>
+      </c>
+      <c r="T44">
+        <v>1.574680929085154</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0.05582068626162334</v>
+      </c>
+      <c r="W44">
+        <v>0.2254700201207244</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.328356978009549</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1612138956386961</v>
+      </c>
+      <c r="C45">
+        <v>22.21994319401492</v>
+      </c>
+      <c r="D45">
+        <v>135.7239431940149</v>
+      </c>
+      <c r="E45">
+        <v>173.304</v>
+      </c>
+      <c r="F45">
+        <v>207.604</v>
+      </c>
+      <c r="G45">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H45">
+        <v>448.5</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>38.6</v>
+      </c>
+      <c r="K45">
+        <v>22.7</v>
+      </c>
+      <c r="L45">
+        <v>15.9</v>
+      </c>
+      <c r="M45">
+        <v>49.57583520000001</v>
+      </c>
+      <c r="N45">
+        <v>-33.67583520000001</v>
+      </c>
+      <c r="O45">
+        <v>-5.724891984000002</v>
+      </c>
+      <c r="P45">
+        <v>-27.95094321600001</v>
+      </c>
+      <c r="Q45">
+        <v>-5.250943216000003</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.11250611787367</v>
+      </c>
+      <c r="T45">
+        <v>1.602306910297175</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.05452253076716698</v>
+      </c>
+      <c r="W45">
+        <v>0.2257800196528005</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.3207207692186292</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1632138956386961</v>
+      </c>
+      <c r="C46">
+        <v>15.21012994080462</v>
+      </c>
+      <c r="D46">
+        <v>133.5421299408046</v>
+      </c>
+      <c r="E46">
+        <v>178.132</v>
+      </c>
+      <c r="F46">
+        <v>212.432</v>
+      </c>
+      <c r="G46">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H46">
+        <v>448.5</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>38.6</v>
+      </c>
+      <c r="K46">
+        <v>22.7</v>
+      </c>
+      <c r="L46">
+        <v>15.9</v>
+      </c>
+      <c r="M46">
+        <v>50.72876160000001</v>
+      </c>
+      <c r="N46">
+        <v>-34.82876160000001</v>
+      </c>
+      <c r="O46">
+        <v>-5.920889472000002</v>
+      </c>
+      <c r="P46">
+        <v>-28.907872128</v>
+      </c>
+      <c r="Q46">
+        <v>-6.207872128000002</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1138222985499856</v>
+      </c>
+      <c r="T46">
+        <v>1.630919533695338</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.05328338234064046</v>
+      </c>
+      <c r="W46">
+        <v>0.2260759282970551</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.3134316608272968</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1652138956386962</v>
+      </c>
+      <c r="C47">
+        <v>8.269353821279225</v>
+      </c>
+      <c r="D47">
+        <v>131.4293538212792</v>
+      </c>
+      <c r="E47">
+        <v>182.96</v>
+      </c>
+      <c r="F47">
+        <v>217.26</v>
+      </c>
+      <c r="G47">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H47">
+        <v>448.5</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>38.6</v>
+      </c>
+      <c r="K47">
+        <v>22.7</v>
+      </c>
+      <c r="L47">
+        <v>15.9</v>
+      </c>
+      <c r="M47">
+        <v>51.881688</v>
+      </c>
+      <c r="N47">
+        <v>-35.98168800000001</v>
+      </c>
+      <c r="O47">
+        <v>-6.116886960000001</v>
+      </c>
+      <c r="P47">
+        <v>-29.86480104</v>
+      </c>
+      <c r="Q47">
+        <v>-7.16480104</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1151863403418035</v>
+      </c>
+      <c r="T47">
+        <v>1.660572616126162</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.05209930717751511</v>
+      </c>
+      <c r="W47">
+        <v>0.2263586854460094</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.3064665128089125</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1672138956386962</v>
+      </c>
+      <c r="C48">
+        <v>1.394389150242915</v>
+      </c>
+      <c r="D48">
+        <v>129.3823891502429</v>
+      </c>
+      <c r="E48">
+        <v>187.788</v>
+      </c>
+      <c r="F48">
+        <v>222.088</v>
+      </c>
+      <c r="G48">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H48">
+        <v>448.5</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>38.6</v>
+      </c>
+      <c r="K48">
+        <v>22.7</v>
+      </c>
+      <c r="L48">
+        <v>15.9</v>
+      </c>
+      <c r="M48">
+        <v>53.03461440000001</v>
+      </c>
+      <c r="N48">
+        <v>-37.13461440000001</v>
+      </c>
+      <c r="O48">
+        <v>-6.312884448000002</v>
+      </c>
+      <c r="P48">
+        <v>-30.82172995200001</v>
+      </c>
+      <c r="Q48">
+        <v>-8.121729952000006</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.116600902199985</v>
+      </c>
+      <c r="T48">
+        <v>1.69132396086924</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.0509667135432213</v>
+      </c>
+      <c r="W48">
+        <v>0.2266291488058788</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.2998041973130665</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1692138956386962</v>
+      </c>
+      <c r="C49">
+        <v>-5.417791883788794</v>
+      </c>
+      <c r="D49">
+        <v>127.3982081162113</v>
+      </c>
+      <c r="E49">
+        <v>192.616</v>
+      </c>
+      <c r="F49">
+        <v>226.916</v>
+      </c>
+      <c r="G49">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H49">
+        <v>448.5</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>38.6</v>
+      </c>
+      <c r="K49">
+        <v>22.7</v>
+      </c>
+      <c r="L49">
+        <v>15.9</v>
+      </c>
+      <c r="M49">
+        <v>54.18754080000001</v>
+      </c>
+      <c r="N49">
+        <v>-38.28754080000001</v>
+      </c>
+      <c r="O49">
+        <v>-6.508881936000002</v>
+      </c>
+      <c r="P49">
+        <v>-31.77865886400001</v>
+      </c>
+      <c r="Q49">
+        <v>-9.078658864000005</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1180688437509281</v>
+      </c>
+      <c r="T49">
+        <v>1.723235733715829</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.04988231538272723</v>
+      </c>
+      <c r="W49">
+        <v>0.2268881030866047</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.2934253846042778</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1712138956386962</v>
+      </c>
+      <c r="C50">
+        <v>-12.17003416216457</v>
+      </c>
+      <c r="D50">
+        <v>125.4739658378354</v>
+      </c>
+      <c r="E50">
+        <v>197.444</v>
+      </c>
+      <c r="F50">
+        <v>231.744</v>
+      </c>
+      <c r="G50">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H50">
+        <v>448.5</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>38.6</v>
+      </c>
+      <c r="K50">
+        <v>22.7</v>
+      </c>
+      <c r="L50">
+        <v>15.9</v>
+      </c>
+      <c r="M50">
+        <v>55.34046720000001</v>
+      </c>
+      <c r="N50">
+        <v>-39.44046720000001</v>
+      </c>
+      <c r="O50">
+        <v>-6.704879424000001</v>
+      </c>
+      <c r="P50">
+        <v>-32.735587776</v>
+      </c>
+      <c r="Q50">
+        <v>-10.035587776</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1195932445922921</v>
+      </c>
+      <c r="T50">
+        <v>1.756374882441134</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.04884310047892042</v>
+      </c>
+      <c r="W50">
+        <v>0.2271362676056338</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.2873123557583553</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1732138956386961</v>
+      </c>
+      <c r="C51">
+        <v>-18.86501324556389</v>
+      </c>
+      <c r="D51">
+        <v>123.6069867544361</v>
+      </c>
+      <c r="E51">
+        <v>202.272</v>
+      </c>
+      <c r="F51">
+        <v>236.572</v>
+      </c>
+      <c r="G51">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H51">
+        <v>448.5</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>38.6</v>
+      </c>
+      <c r="K51">
+        <v>22.7</v>
+      </c>
+      <c r="L51">
+        <v>15.9</v>
+      </c>
+      <c r="M51">
+        <v>56.4933936</v>
+      </c>
+      <c r="N51">
+        <v>-40.59339360000001</v>
+      </c>
+      <c r="O51">
+        <v>-6.900876912000001</v>
+      </c>
+      <c r="P51">
+        <v>-33.692516688</v>
+      </c>
+      <c r="Q51">
+        <v>-10.992516688</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1211774258588077</v>
+      </c>
+      <c r="T51">
+        <v>1.790813605626254</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.04784630250996286</v>
+      </c>
+      <c r="W51">
+        <v>0.2273743029606209</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.2814488382938991</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1752138956386962</v>
+      </c>
+      <c r="C52">
+        <v>-25.50524778627113</v>
+      </c>
+      <c r="D52">
+        <v>121.7947522137289</v>
+      </c>
+      <c r="E52">
+        <v>207.1</v>
+      </c>
+      <c r="F52">
+        <v>241.4</v>
+      </c>
+      <c r="G52">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H52">
+        <v>448.5</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>38.6</v>
+      </c>
+      <c r="K52">
+        <v>22.7</v>
+      </c>
+      <c r="L52">
+        <v>15.9</v>
+      </c>
+      <c r="M52">
+        <v>57.64632</v>
+      </c>
+      <c r="N52">
+        <v>-41.74632</v>
+      </c>
+      <c r="O52">
+        <v>-7.096874400000001</v>
+      </c>
+      <c r="P52">
+        <v>-34.64944560000001</v>
+      </c>
+      <c r="Q52">
+        <v>-11.9494456</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1228249743759838</v>
+      </c>
+      <c r="T52">
+        <v>1.826629877738779</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.04688937645976361</v>
+      </c>
+      <c r="W52">
+        <v>0.2276028169014085</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.2758198615280212</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1772138956386961</v>
+      </c>
+      <c r="C53">
+        <v>-32.09311086434894</v>
+      </c>
+      <c r="D53">
+        <v>120.0348891356511</v>
+      </c>
+      <c r="E53">
+        <v>211.928</v>
+      </c>
+      <c r="F53">
+        <v>246.228</v>
+      </c>
+      <c r="G53">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H53">
+        <v>448.5</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>38.6</v>
+      </c>
+      <c r="K53">
+        <v>22.7</v>
+      </c>
+      <c r="L53">
+        <v>15.9</v>
+      </c>
+      <c r="M53">
+        <v>58.79924640000001</v>
+      </c>
+      <c r="N53">
+        <v>-42.89924640000001</v>
+      </c>
+      <c r="O53">
+        <v>-7.292871888000002</v>
+      </c>
+      <c r="P53">
+        <v>-35.60637451200001</v>
+      </c>
+      <c r="Q53">
+        <v>-12.90637451200001</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1245397697714121</v>
+      </c>
+      <c r="T53">
+        <v>1.863908038508958</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.04596997692133686</v>
+      </c>
+      <c r="W53">
+        <v>0.2278223695111848</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.2704116289490404</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1792138956386961</v>
+      </c>
+      <c r="C54">
+        <v>-38.63084035500444</v>
+      </c>
+      <c r="D54">
+        <v>118.3251596449956</v>
+      </c>
+      <c r="E54">
+        <v>216.756</v>
+      </c>
+      <c r="F54">
+        <v>251.056</v>
+      </c>
+      <c r="G54">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H54">
+        <v>448.5</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>38.6</v>
+      </c>
+      <c r="K54">
+        <v>22.7</v>
+      </c>
+      <c r="L54">
+        <v>15.9</v>
+      </c>
+      <c r="M54">
+        <v>59.95217280000001</v>
+      </c>
+      <c r="N54">
+        <v>-44.05217280000001</v>
+      </c>
+      <c r="O54">
+        <v>-7.488869376000002</v>
+      </c>
+      <c r="P54">
+        <v>-36.563303424</v>
+      </c>
+      <c r="Q54">
+        <v>-13.863303424</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1263260149749832</v>
+      </c>
+      <c r="T54">
+        <v>1.902739455977895</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.04508593890361885</v>
+      </c>
+      <c r="W54">
+        <v>0.2280334777898158</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.265211405315405</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1812138956386961</v>
+      </c>
+      <c r="C55">
+        <v>-45.12054842238553</v>
+      </c>
+      <c r="D55">
+        <v>116.6634515776145</v>
+      </c>
+      <c r="E55">
+        <v>221.584</v>
+      </c>
+      <c r="F55">
+        <v>255.884</v>
+      </c>
+      <c r="G55">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H55">
+        <v>448.5</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>38.6</v>
+      </c>
+      <c r="K55">
+        <v>22.7</v>
+      </c>
+      <c r="L55">
+        <v>15.9</v>
+      </c>
+      <c r="M55">
+        <v>61.10509920000001</v>
+      </c>
+      <c r="N55">
+        <v>-45.20509920000001</v>
+      </c>
+      <c r="O55">
+        <v>-7.684866864000002</v>
+      </c>
+      <c r="P55">
+        <v>-37.52023233600001</v>
+      </c>
+      <c r="Q55">
+        <v>-14.820232336</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1281882706127487</v>
+      </c>
+      <c r="T55">
+        <v>1.94322327419019</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.04423526081109774</v>
+      </c>
+      <c r="W55">
+        <v>0.2282366197183099</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.260207416535869</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1832138956386961</v>
+      </c>
+      <c r="C56">
+        <v>-51.56423022449539</v>
+      </c>
+      <c r="D56">
+        <v>115.0477697755047</v>
+      </c>
+      <c r="E56">
+        <v>226.412</v>
+      </c>
+      <c r="F56">
+        <v>260.712</v>
+      </c>
+      <c r="G56">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H56">
+        <v>448.5</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>38.6</v>
+      </c>
+      <c r="K56">
+        <v>22.7</v>
+      </c>
+      <c r="L56">
+        <v>15.9</v>
+      </c>
+      <c r="M56">
+        <v>62.25802560000002</v>
+      </c>
+      <c r="N56">
+        <v>-46.35802560000002</v>
+      </c>
+      <c r="O56">
+        <v>-7.880864352000004</v>
+      </c>
+      <c r="P56">
+        <v>-38.47716124800002</v>
+      </c>
+      <c r="Q56">
+        <v>-15.77716124800001</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.130131493886939</v>
+      </c>
+      <c r="T56">
+        <v>1.985467258411717</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.04341608931459592</v>
+      </c>
+      <c r="W56">
+        <v>0.2284322378716745</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.2553887606740937</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1852138956386962</v>
+      </c>
+      <c r="C57">
+        <v>-57.96377190465677</v>
+      </c>
+      <c r="D57">
+        <v>113.4762280953432</v>
+      </c>
+      <c r="E57">
+        <v>231.24</v>
+      </c>
+      <c r="F57">
+        <v>265.54</v>
+      </c>
+      <c r="G57">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H57">
+        <v>448.5</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>38.6</v>
+      </c>
+      <c r="K57">
+        <v>22.7</v>
+      </c>
+      <c r="L57">
+        <v>15.9</v>
+      </c>
+      <c r="M57">
+        <v>63.41095200000001</v>
+      </c>
+      <c r="N57">
+        <v>-47.51095200000001</v>
+      </c>
+      <c r="O57">
+        <v>-8.076861840000003</v>
+      </c>
+      <c r="P57">
+        <v>-39.43409016000001</v>
+      </c>
+      <c r="Q57">
+        <v>-16.73409016000001</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1321610826399821</v>
+      </c>
+      <c r="T57">
+        <v>2.029588753043088</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.04262670587251236</v>
+      </c>
+      <c r="W57">
+        <v>0.2286207426376441</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.2507453286618374</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1872138956386962</v>
+      </c>
+      <c r="C58">
+        <v>-64.32095793682717</v>
+      </c>
+      <c r="D58">
+        <v>111.9470420631729</v>
+      </c>
+      <c r="E58">
+        <v>236.068</v>
+      </c>
+      <c r="F58">
+        <v>270.3680000000001</v>
+      </c>
+      <c r="G58">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H58">
+        <v>448.5</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>38.6</v>
+      </c>
+      <c r="K58">
+        <v>22.7</v>
+      </c>
+      <c r="L58">
+        <v>15.9</v>
+      </c>
+      <c r="M58">
+        <v>64.56387840000002</v>
+      </c>
+      <c r="N58">
+        <v>-48.66387840000002</v>
+      </c>
+      <c r="O58">
+        <v>-8.272859328000004</v>
+      </c>
+      <c r="P58">
+        <v>-40.39101907200002</v>
+      </c>
+      <c r="Q58">
+        <v>-17.69101907200002</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1342829254272544</v>
+      </c>
+      <c r="T58">
+        <v>2.075715770157704</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.04186551469621749</v>
+      </c>
+      <c r="W58">
+        <v>0.2288025150905433</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.2462677335071617</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1892138956386962</v>
+      </c>
+      <c r="C59">
+        <v>-70.63747788490531</v>
+      </c>
+      <c r="D59">
+        <v>110.4585221150947</v>
+      </c>
+      <c r="E59">
+        <v>240.896</v>
+      </c>
+      <c r="F59">
+        <v>275.196</v>
+      </c>
+      <c r="G59">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H59">
+        <v>448.5</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>38.6</v>
+      </c>
+      <c r="K59">
+        <v>22.7</v>
+      </c>
+      <c r="L59">
+        <v>15.9</v>
+      </c>
+      <c r="M59">
+        <v>65.71680480000001</v>
+      </c>
+      <c r="N59">
+        <v>-49.81680480000001</v>
+      </c>
+      <c r="O59">
+        <v>-8.468856816000002</v>
+      </c>
+      <c r="P59">
+        <v>-41.347947984</v>
+      </c>
+      <c r="Q59">
+        <v>-18.647947984</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1365034585767254</v>
+      </c>
+      <c r="T59">
+        <v>2.123988229928813</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.04113103198224877</v>
+      </c>
+      <c r="W59">
+        <v>0.228977909562639</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.2419472469544045</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1912138956386961</v>
+      </c>
+      <c r="C60">
+        <v>-76.9149326298577</v>
+      </c>
+      <c r="D60">
+        <v>109.0090673701423</v>
+      </c>
+      <c r="E60">
+        <v>245.724</v>
+      </c>
+      <c r="F60">
+        <v>280.024</v>
+      </c>
+      <c r="G60">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H60">
+        <v>448.5</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>38.6</v>
+      </c>
+      <c r="K60">
+        <v>22.7</v>
+      </c>
+      <c r="L60">
+        <v>15.9</v>
+      </c>
+      <c r="M60">
+        <v>66.8697312</v>
+      </c>
+      <c r="N60">
+        <v>-50.96973120000001</v>
+      </c>
+      <c r="O60">
+        <v>-8.664854304000002</v>
+      </c>
+      <c r="P60">
+        <v>-42.304876896</v>
+      </c>
+      <c r="Q60">
+        <v>-19.604876896</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1388297313999807</v>
+      </c>
+      <c r="T60">
+        <v>2.17455937826045</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.0404218762584169</v>
+      </c>
+      <c r="W60">
+        <v>0.2291472559494901</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.23777574269657</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1932138956386961</v>
+      </c>
+      <c r="C61">
+        <v>-83.15484011291483</v>
+      </c>
+      <c r="D61">
+        <v>107.5971598870851</v>
+      </c>
+      <c r="E61">
+        <v>250.552</v>
+      </c>
+      <c r="F61">
+        <v>284.852</v>
+      </c>
+      <c r="G61">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H61">
+        <v>448.5</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>38.6</v>
+      </c>
+      <c r="K61">
+        <v>22.7</v>
+      </c>
+      <c r="L61">
+        <v>15.9</v>
+      </c>
+      <c r="M61">
+        <v>68.0226576</v>
+      </c>
+      <c r="N61">
+        <v>-52.1226576</v>
+      </c>
+      <c r="O61">
+        <v>-8.860851792000002</v>
+      </c>
+      <c r="P61">
+        <v>-43.26180580800001</v>
+      </c>
+      <c r="Q61">
+        <v>-20.561805808</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1412694809463217</v>
+      </c>
+      <c r="T61">
+        <v>2.227597411876559</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.03973675971166407</v>
+      </c>
+      <c r="W61">
+        <v>0.2293108617808546</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.2337456453627298</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1952138956386961</v>
+      </c>
+      <c r="C62">
+        <v>-89.35864063815242</v>
+      </c>
+      <c r="D62">
+        <v>106.2213593618476</v>
+      </c>
+      <c r="E62">
+        <v>255.38</v>
+      </c>
+      <c r="F62">
+        <v>289.68</v>
+      </c>
+      <c r="G62">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H62">
+        <v>448.5</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>38.6</v>
+      </c>
+      <c r="K62">
+        <v>22.7</v>
+      </c>
+      <c r="L62">
+        <v>15.9</v>
+      </c>
+      <c r="M62">
+        <v>69.175584</v>
+      </c>
+      <c r="N62">
+        <v>-53.275584</v>
+      </c>
+      <c r="O62">
+        <v>-9.056849280000002</v>
+      </c>
+      <c r="P62">
+        <v>-44.21873472</v>
+      </c>
+      <c r="Q62">
+        <v>-21.51873472</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1438312179699798</v>
+      </c>
+      <c r="T62">
+        <v>2.283287347173473</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.03907448038313634</v>
+      </c>
+      <c r="W62">
+        <v>0.2294690140845071</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.2298498846066843</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1972138956386962</v>
+      </c>
+      <c r="C63">
+        <v>-95.52770177339664</v>
+      </c>
+      <c r="D63">
+        <v>104.8802982266033</v>
+      </c>
+      <c r="E63">
+        <v>260.208</v>
+      </c>
+      <c r="F63">
+        <v>294.508</v>
+      </c>
+      <c r="G63">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H63">
+        <v>448.5</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>38.6</v>
+      </c>
+      <c r="K63">
+        <v>22.7</v>
+      </c>
+      <c r="L63">
+        <v>15.9</v>
+      </c>
+      <c r="M63">
+        <v>70.3285104</v>
+      </c>
+      <c r="N63">
+        <v>-54.4285104</v>
+      </c>
+      <c r="O63">
+        <v>-9.252846768000001</v>
+      </c>
+      <c r="P63">
+        <v>-45.175663632</v>
+      </c>
+      <c r="Q63">
+        <v>-22.47566363199999</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1465243261230562</v>
+      </c>
+      <c r="T63">
+        <v>2.341833176588178</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.03843391513095377</v>
+      </c>
+      <c r="W63">
+        <v>0.2296219810667283</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.2260818537114928</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1992138956386962</v>
+      </c>
+      <c r="C64">
+        <v>-101.6633228845108</v>
+      </c>
+      <c r="D64">
+        <v>103.5726771154893</v>
+      </c>
+      <c r="E64">
+        <v>265.036</v>
+      </c>
+      <c r="F64">
+        <v>299.336</v>
+      </c>
+      <c r="G64">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H64">
+        <v>448.5</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>38.6</v>
+      </c>
+      <c r="K64">
+        <v>22.7</v>
+      </c>
+      <c r="L64">
+        <v>15.9</v>
+      </c>
+      <c r="M64">
+        <v>71.48143680000001</v>
+      </c>
+      <c r="N64">
+        <v>-55.58143680000001</v>
+      </c>
+      <c r="O64">
+        <v>-9.448844256000003</v>
+      </c>
+      <c r="P64">
+        <v>-46.13259254400001</v>
+      </c>
+      <c r="Q64">
+        <v>-23.43259254400001</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.149359176810505</v>
+      </c>
+      <c r="T64">
+        <v>2.403460365445762</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.0378140132740029</v>
+      </c>
+      <c r="W64">
+        <v>0.2297700136301681</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.2224353722000171</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2012138956386961</v>
+      </c>
+      <c r="C65">
+        <v>-107.7667393346634</v>
+      </c>
+      <c r="D65">
+        <v>102.2972606653366</v>
+      </c>
+      <c r="E65">
+        <v>269.864</v>
+      </c>
+      <c r="F65">
+        <v>304.164</v>
+      </c>
+      <c r="G65">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H65">
+        <v>448.5</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>38.6</v>
+      </c>
+      <c r="K65">
+        <v>22.7</v>
+      </c>
+      <c r="L65">
+        <v>15.9</v>
+      </c>
+      <c r="M65">
+        <v>72.6343632</v>
+      </c>
+      <c r="N65">
+        <v>-56.7343632</v>
+      </c>
+      <c r="O65">
+        <v>-9.644841744000001</v>
+      </c>
+      <c r="P65">
+        <v>-47.089521456</v>
+      </c>
+      <c r="Q65">
+        <v>-24.389521456</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1523472626702484</v>
+      </c>
+      <c r="T65">
+        <v>2.468418753701052</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.03721379084108223</v>
+      </c>
+      <c r="W65">
+        <v>0.2299133467471496</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.218904652006366</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2032138956386961</v>
+      </c>
+      <c r="C66">
+        <v>-113.8391263771083</v>
+      </c>
+      <c r="D66">
+        <v>101.0528736228917</v>
+      </c>
+      <c r="E66">
+        <v>274.692</v>
+      </c>
+      <c r="F66">
+        <v>308.992</v>
+      </c>
+      <c r="G66">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H66">
+        <v>448.5</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>38.6</v>
+      </c>
+      <c r="K66">
+        <v>22.7</v>
+      </c>
+      <c r="L66">
+        <v>15.9</v>
+      </c>
+      <c r="M66">
+        <v>73.78728960000001</v>
+      </c>
+      <c r="N66">
+        <v>-57.88728960000001</v>
+      </c>
+      <c r="O66">
+        <v>-9.840839232000002</v>
+      </c>
+      <c r="P66">
+        <v>-48.04645036800001</v>
+      </c>
+      <c r="Q66">
+        <v>-25.34645036800001</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1555013532999775</v>
+      </c>
+      <c r="T66">
+        <v>2.536985941303859</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.03663232535919032</v>
+      </c>
+      <c r="W66">
+        <v>0.2300522007042254</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.2154842668187665</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2052138956386962</v>
+      </c>
+      <c r="C67">
+        <v>-119.8816027672565</v>
+      </c>
+      <c r="D67">
+        <v>99.83839723274352</v>
+      </c>
+      <c r="E67">
+        <v>279.52</v>
+      </c>
+      <c r="F67">
+        <v>313.82</v>
+      </c>
+      <c r="G67">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H67">
+        <v>448.5</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>38.6</v>
+      </c>
+      <c r="K67">
+        <v>22.7</v>
+      </c>
+      <c r="L67">
+        <v>15.9</v>
+      </c>
+      <c r="M67">
+        <v>74.94021600000001</v>
+      </c>
+      <c r="N67">
+        <v>-59.04021600000001</v>
+      </c>
+      <c r="O67">
+        <v>-10.03683672</v>
+      </c>
+      <c r="P67">
+        <v>-49.00337928</v>
+      </c>
+      <c r="Q67">
+        <v>-26.30337928</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1588356776799769</v>
+      </c>
+      <c r="T67">
+        <v>2.609471253912541</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.03606875112289508</v>
+      </c>
+      <c r="W67">
+        <v>0.2301867822318527</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.2121691242523239</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2072138956386962</v>
+      </c>
+      <c r="C68">
+        <v>-125.895234117379</v>
+      </c>
+      <c r="D68">
+        <v>98.65276588262101</v>
+      </c>
+      <c r="E68">
+        <v>284.348</v>
+      </c>
+      <c r="F68">
+        <v>318.648</v>
+      </c>
+      <c r="G68">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H68">
+        <v>448.5</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>38.6</v>
+      </c>
+      <c r="K68">
+        <v>22.7</v>
+      </c>
+      <c r="L68">
+        <v>15.9</v>
+      </c>
+      <c r="M68">
+        <v>76.0931424</v>
+      </c>
+      <c r="N68">
+        <v>-60.19314240000001</v>
+      </c>
+      <c r="O68">
+        <v>-10.232834208</v>
+      </c>
+      <c r="P68">
+        <v>-49.96030819200001</v>
+      </c>
+      <c r="Q68">
+        <v>-27.260308192</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1623661387882115</v>
+      </c>
+      <c r="T68">
+        <v>2.686220408439381</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.0355222548937603</v>
+      </c>
+      <c r="W68">
+        <v>0.2303172855313701</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.2089544405515312</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2092138956386961</v>
+      </c>
+      <c r="C69">
+        <v>-131.8810360150808</v>
+      </c>
+      <c r="D69">
+        <v>97.49496398491921</v>
+      </c>
+      <c r="E69">
+        <v>289.176</v>
+      </c>
+      <c r="F69">
+        <v>323.476</v>
+      </c>
+      <c r="G69">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H69">
+        <v>448.5</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>38.6</v>
+      </c>
+      <c r="K69">
+        <v>22.7</v>
+      </c>
+      <c r="L69">
+        <v>15.9</v>
+      </c>
+      <c r="M69">
+        <v>77.2460688</v>
+      </c>
+      <c r="N69">
+        <v>-61.3460688</v>
+      </c>
+      <c r="O69">
+        <v>-10.428831696</v>
+      </c>
+      <c r="P69">
+        <v>-50.917237104</v>
+      </c>
+      <c r="Q69">
+        <v>-28.217237104</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1661105672363391</v>
+      </c>
+      <c r="T69">
+        <v>2.767621026876938</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.03499207198489821</v>
+      </c>
+      <c r="W69">
+        <v>0.2304438932100063</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.2058357175582247</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2112138956386962</v>
+      </c>
+      <c r="C70">
+        <v>-137.8399769247304</v>
+      </c>
+      <c r="D70">
+        <v>96.36402307526969</v>
+      </c>
+      <c r="E70">
+        <v>294.004</v>
+      </c>
+      <c r="F70">
+        <v>328.304</v>
+      </c>
+      <c r="G70">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H70">
+        <v>448.5</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>38.6</v>
+      </c>
+      <c r="K70">
+        <v>22.7</v>
+      </c>
+      <c r="L70">
+        <v>15.9</v>
+      </c>
+      <c r="M70">
+        <v>78.39899520000002</v>
+      </c>
+      <c r="N70">
+        <v>-62.49899520000002</v>
+      </c>
+      <c r="O70">
+        <v>-10.624829184</v>
+      </c>
+      <c r="P70">
+        <v>-51.87416601600002</v>
+      </c>
+      <c r="Q70">
+        <v>-29.17416601600002</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.1700890224624748</v>
+      </c>
+      <c r="T70">
+        <v>2.854109183966842</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.03447748269100264</v>
+      </c>
+      <c r="W70">
+        <v>0.2305667771333886</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.2028087217117802</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2132138956386962</v>
+      </c>
+      <c r="C71">
+        <v>-143.7729808892641</v>
+      </c>
+      <c r="D71">
+        <v>95.25901911073593</v>
+      </c>
+      <c r="E71">
+        <v>298.8320000000001</v>
+      </c>
+      <c r="F71">
+        <v>333.1320000000001</v>
+      </c>
+      <c r="G71">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H71">
+        <v>448.5</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>38.6</v>
+      </c>
+      <c r="K71">
+        <v>22.7</v>
+      </c>
+      <c r="L71">
+        <v>15.9</v>
+      </c>
+      <c r="M71">
+        <v>79.55192160000001</v>
+      </c>
+      <c r="N71">
+        <v>-63.65192160000002</v>
+      </c>
+      <c r="O71">
+        <v>-10.820826672</v>
+      </c>
+      <c r="P71">
+        <v>-52.83109492800001</v>
+      </c>
+      <c r="Q71">
+        <v>-30.13109492800001</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.1743241522193288</v>
+      </c>
+      <c r="T71">
+        <v>2.946177222159322</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.0339778090288142</v>
+      </c>
+      <c r="W71">
+        <v>0.2306860992039192</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.1998694648753776</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2152138956386961</v>
+      </c>
+      <c r="C72">
+        <v>-149.6809300482105</v>
+      </c>
+      <c r="D72">
+        <v>94.17906995178953</v>
+      </c>
+      <c r="E72">
+        <v>303.66</v>
+      </c>
+      <c r="F72">
+        <v>337.96</v>
+      </c>
+      <c r="G72">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H72">
+        <v>448.5</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>38.6</v>
+      </c>
+      <c r="K72">
+        <v>22.7</v>
+      </c>
+      <c r="L72">
+        <v>15.9</v>
+      </c>
+      <c r="M72">
+        <v>80.70484800000001</v>
+      </c>
+      <c r="N72">
+        <v>-64.80484800000002</v>
+      </c>
+      <c r="O72">
+        <v>-11.01682416</v>
+      </c>
+      <c r="P72">
+        <v>-53.78802384000002</v>
+      </c>
+      <c r="Q72">
+        <v>-31.08802384000001</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.1788416239599731</v>
+      </c>
+      <c r="T72">
+        <v>3.044383129564632</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.033492411756974</v>
+      </c>
+      <c r="W72">
+        <v>0.2308020120724346</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.1970141868057294</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2172138956386962</v>
+      </c>
+      <c r="C73">
+        <v>-155.5646669863524</v>
+      </c>
+      <c r="D73">
+        <v>93.1233330136476</v>
+      </c>
+      <c r="E73">
+        <v>308.488</v>
+      </c>
+      <c r="F73">
+        <v>342.788</v>
+      </c>
+      <c r="G73">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H73">
+        <v>448.5</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>38.6</v>
+      </c>
+      <c r="K73">
+        <v>22.7</v>
+      </c>
+      <c r="L73">
+        <v>15.9</v>
+      </c>
+      <c r="M73">
+        <v>81.85777440000001</v>
+      </c>
+      <c r="N73">
+        <v>-65.95777440000001</v>
+      </c>
+      <c r="O73">
+        <v>-11.212821648</v>
+      </c>
+      <c r="P73">
+        <v>-54.744952752</v>
+      </c>
+      <c r="Q73">
+        <v>-32.044952752</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.1836706454758342</v>
+      </c>
+      <c r="T73">
+        <v>3.149361858170308</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.03302068764772084</v>
+      </c>
+      <c r="W73">
+        <v>0.2309146597897243</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.1942393391042403</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2192138956386961</v>
+      </c>
+      <c r="C74">
+        <v>-161.424996926172</v>
+      </c>
+      <c r="D74">
+        <v>92.09100307382805</v>
+      </c>
+      <c r="E74">
+        <v>313.316</v>
+      </c>
+      <c r="F74">
+        <v>347.616</v>
+      </c>
+      <c r="G74">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H74">
+        <v>448.5</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>38.6</v>
+      </c>
+      <c r="K74">
+        <v>22.7</v>
+      </c>
+      <c r="L74">
+        <v>15.9</v>
+      </c>
+      <c r="M74">
+        <v>83.0107008</v>
+      </c>
+      <c r="N74">
+        <v>-67.11070079999999</v>
+      </c>
+      <c r="O74">
+        <v>-11.408819136</v>
+      </c>
+      <c r="P74">
+        <v>-55.70188166399999</v>
+      </c>
+      <c r="Q74">
+        <v>-33.00188166399999</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.1888445970999711</v>
+      </c>
+      <c r="T74">
+        <v>3.261839067390676</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.03256206698594695</v>
+      </c>
+      <c r="W74">
+        <v>0.2310241784037559</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.1915415705055704</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2212138956386961</v>
+      </c>
+      <c r="C75">
+        <v>-167.2626897760657</v>
+      </c>
+      <c r="D75">
+        <v>91.08131022393431</v>
+      </c>
+      <c r="E75">
+        <v>318.144</v>
+      </c>
+      <c r="F75">
+        <v>352.444</v>
+      </c>
+      <c r="G75">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H75">
+        <v>448.5</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>38.6</v>
+      </c>
+      <c r="K75">
+        <v>22.7</v>
+      </c>
+      <c r="L75">
+        <v>15.9</v>
+      </c>
+      <c r="M75">
+        <v>84.16362720000001</v>
+      </c>
+      <c r="N75">
+        <v>-68.2636272</v>
+      </c>
+      <c r="O75">
+        <v>-11.604816624</v>
+      </c>
+      <c r="P75">
+        <v>-56.658810576</v>
+      </c>
+      <c r="Q75">
+        <v>-33.958810576</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.19440180439997</v>
+      </c>
+      <c r="T75">
+        <v>3.382647921738479</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.03211601127381068</v>
+      </c>
+      <c r="W75">
+        <v>0.231130696507814</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.188917713375357</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2232138956386961</v>
+      </c>
+      <c r="C76">
+        <v>-173.0784820452815</v>
+      </c>
+      <c r="D76">
+        <v>90.09351795471854</v>
+      </c>
+      <c r="E76">
+        <v>322.972</v>
+      </c>
+      <c r="F76">
+        <v>357.272</v>
+      </c>
+      <c r="G76">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H76">
+        <v>448.5</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>38.6</v>
+      </c>
+      <c r="K76">
+        <v>22.7</v>
+      </c>
+      <c r="L76">
+        <v>15.9</v>
+      </c>
+      <c r="M76">
+        <v>85.31655360000001</v>
+      </c>
+      <c r="N76">
+        <v>-69.41655360000001</v>
+      </c>
+      <c r="O76">
+        <v>-11.800814112</v>
+      </c>
+      <c r="P76">
+        <v>-57.61573948800001</v>
+      </c>
+      <c r="Q76">
+        <v>-34.91573948800001</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2003864891845843</v>
+      </c>
+      <c r="T76">
+        <v>3.512749764882267</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.03168201112146189</v>
+      </c>
+      <c r="W76">
+        <v>0.2312343357441949</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.1863647713027169</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2252138956386961</v>
+      </c>
+      <c r="C77">
+        <v>-178.8730786355843</v>
+      </c>
+      <c r="D77">
+        <v>89.12692136441569</v>
+      </c>
+      <c r="E77">
+        <v>327.8</v>
+      </c>
+      <c r="F77">
+        <v>362.1</v>
+      </c>
+      <c r="G77">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H77">
+        <v>448.5</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>38.6</v>
+      </c>
+      <c r="K77">
+        <v>22.7</v>
+      </c>
+      <c r="L77">
+        <v>15.9</v>
+      </c>
+      <c r="M77">
+        <v>86.46948</v>
+      </c>
+      <c r="N77">
+        <v>-70.56948</v>
+      </c>
+      <c r="O77">
+        <v>-11.9968116</v>
+      </c>
+      <c r="P77">
+        <v>-58.5726684</v>
+      </c>
+      <c r="Q77">
+        <v>-35.87266839999999</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2068499487519677</v>
+      </c>
+      <c r="T77">
+        <v>3.653259755477558</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.03125958430650907</v>
+      </c>
+      <c r="W77">
+        <v>0.2313352112676056</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.1838799076853476</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2272138956386962</v>
+      </c>
+      <c r="C78">
+        <v>-184.6471545188124</v>
+      </c>
+      <c r="D78">
+        <v>88.18084548118757</v>
+      </c>
+      <c r="E78">
+        <v>332.628</v>
+      </c>
+      <c r="F78">
+        <v>366.928</v>
+      </c>
+      <c r="G78">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H78">
+        <v>448.5</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>38.6</v>
+      </c>
+      <c r="K78">
+        <v>22.7</v>
+      </c>
+      <c r="L78">
+        <v>15.9</v>
+      </c>
+      <c r="M78">
+        <v>87.6224064</v>
+      </c>
+      <c r="N78">
+        <v>-71.72240640000001</v>
+      </c>
+      <c r="O78">
+        <v>-12.192809088</v>
+      </c>
+      <c r="P78">
+        <v>-59.52959731200001</v>
+      </c>
+      <c r="Q78">
+        <v>-36.829597312</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2138520299499663</v>
+      </c>
+      <c r="T78">
+        <v>3.805478911955789</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.03084827398668658</v>
+      </c>
+      <c r="W78">
+        <v>0.2314334321719793</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.1814604352158034</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2292138956386962</v>
+      </c>
+      <c r="C79">
+        <v>-190.4013563087124</v>
+      </c>
+      <c r="D79">
+        <v>87.25464369128765</v>
+      </c>
+      <c r="E79">
+        <v>337.456</v>
+      </c>
+      <c r="F79">
+        <v>371.756</v>
+      </c>
+      <c r="G79">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H79">
+        <v>448.5</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>38.6</v>
+      </c>
+      <c r="K79">
+        <v>22.7</v>
+      </c>
+      <c r="L79">
+        <v>15.9</v>
+      </c>
+      <c r="M79">
+        <v>88.77533280000002</v>
+      </c>
+      <c r="N79">
+        <v>-72.87533280000002</v>
+      </c>
+      <c r="O79">
+        <v>-12.38880657600001</v>
+      </c>
+      <c r="P79">
+        <v>-60.48652622400002</v>
+      </c>
+      <c r="Q79">
+        <v>-37.78652622400001</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2214629877738779</v>
+      </c>
+      <c r="T79">
+        <v>3.970934516823432</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.03044764705179454</v>
+      </c>
+      <c r="W79">
+        <v>0.2315291018840315</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.1791038061870266</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2312138956386962</v>
+      </c>
+      <c r="C80">
+        <v>-196.1363037347458</v>
+      </c>
+      <c r="D80">
+        <v>86.34769626525424</v>
+      </c>
+      <c r="E80">
+        <v>342.284</v>
+      </c>
+      <c r="F80">
+        <v>376.584</v>
+      </c>
+      <c r="G80">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H80">
+        <v>448.5</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>38.6</v>
+      </c>
+      <c r="K80">
+        <v>22.7</v>
+      </c>
+      <c r="L80">
+        <v>15.9</v>
+      </c>
+      <c r="M80">
+        <v>89.9282592</v>
+      </c>
+      <c r="N80">
+        <v>-74.02825920000001</v>
+      </c>
+      <c r="O80">
+        <v>-12.584804064</v>
+      </c>
+      <c r="P80">
+        <v>-61.443455136</v>
+      </c>
+      <c r="Q80">
+        <v>-38.743455136</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.2297658508545087</v>
+      </c>
+      <c r="T80">
+        <v>4.151431540315407</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.03005729260241257</v>
+      </c>
+      <c r="W80">
+        <v>0.2316223185265439</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.1768076035436033</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2332138956386962</v>
+      </c>
+      <c r="C81">
+        <v>-201.8525910249272</v>
+      </c>
+      <c r="D81">
+        <v>85.45940897507282</v>
+      </c>
+      <c r="E81">
+        <v>347.112</v>
+      </c>
+      <c r="F81">
+        <v>381.412</v>
+      </c>
+      <c r="G81">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H81">
+        <v>448.5</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>38.6</v>
+      </c>
+      <c r="K81">
+        <v>22.7</v>
+      </c>
+      <c r="L81">
+        <v>15.9</v>
+      </c>
+      <c r="M81">
+        <v>91.08118560000001</v>
+      </c>
+      <c r="N81">
+        <v>-75.18118560000002</v>
+      </c>
+      <c r="O81">
+        <v>-12.78080155200001</v>
+      </c>
+      <c r="P81">
+        <v>-62.40038404800001</v>
+      </c>
+      <c r="Q81">
+        <v>-39.70038404800001</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.2388594627999615</v>
+      </c>
+      <c r="T81">
+        <v>4.349118756520903</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.02967682054415418</v>
+      </c>
+      <c r="W81">
+        <v>0.231713175254056</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.1745695326126715</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2352138956386961</v>
+      </c>
+      <c r="C82">
+        <v>-207.5507882041763</v>
+      </c>
+      <c r="D82">
+        <v>84.58921179582366</v>
+      </c>
+      <c r="E82">
+        <v>351.94</v>
+      </c>
+      <c r="F82">
+        <v>386.24</v>
+      </c>
+      <c r="G82">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H82">
+        <v>448.5</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>38.6</v>
+      </c>
+      <c r="K82">
+        <v>22.7</v>
+      </c>
+      <c r="L82">
+        <v>15.9</v>
+      </c>
+      <c r="M82">
+        <v>92.23411200000001</v>
+      </c>
+      <c r="N82">
+        <v>-76.334112</v>
+      </c>
+      <c r="O82">
+        <v>-12.97679904</v>
+      </c>
+      <c r="P82">
+        <v>-63.35731296</v>
+      </c>
+      <c r="Q82">
+        <v>-40.65731296</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.2488624359399596</v>
+      </c>
+      <c r="T82">
+        <v>4.566574694346948</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.02930586028735225</v>
+      </c>
+      <c r="W82">
+        <v>0.2318017605633803</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.1723874134550133</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2372138956386962</v>
+      </c>
+      <c r="C83">
+        <v>-213.2314423141472</v>
+      </c>
+      <c r="D83">
+        <v>83.73655768585284</v>
+      </c>
+      <c r="E83">
+        <v>356.768</v>
+      </c>
+      <c r="F83">
+        <v>391.068</v>
+      </c>
+      <c r="G83">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H83">
+        <v>448.5</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>38.6</v>
+      </c>
+      <c r="K83">
+        <v>22.7</v>
+      </c>
+      <c r="L83">
+        <v>15.9</v>
+      </c>
+      <c r="M83">
+        <v>93.38703840000001</v>
+      </c>
+      <c r="N83">
+        <v>-77.48703840000002</v>
+      </c>
+      <c r="O83">
+        <v>-13.172796528</v>
+      </c>
+      <c r="P83">
+        <v>-64.31424187200001</v>
+      </c>
+      <c r="Q83">
+        <v>-41.61424187200001</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.2599183536210101</v>
+      </c>
+      <c r="T83">
+        <v>4.806920730891524</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.02894405954306395</v>
+      </c>
+      <c r="W83">
+        <v>0.2318881585811163</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.170259173782729</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2392138956386962</v>
+      </c>
+      <c r="C84">
+        <v>-218.8950785600172</v>
+      </c>
+      <c r="D84">
+        <v>82.9009214399828</v>
+      </c>
+      <c r="E84">
+        <v>361.596</v>
+      </c>
+      <c r="F84">
+        <v>395.896</v>
+      </c>
+      <c r="G84">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H84">
+        <v>448.5</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>38.6</v>
+      </c>
+      <c r="K84">
+        <v>22.7</v>
+      </c>
+      <c r="L84">
+        <v>15.9</v>
+      </c>
+      <c r="M84">
+        <v>94.53996480000001</v>
+      </c>
+      <c r="N84">
+        <v>-78.6399648</v>
+      </c>
+      <c r="O84">
+        <v>-13.368794016</v>
+      </c>
+      <c r="P84">
+        <v>-65.27117078400001</v>
+      </c>
+      <c r="Q84">
+        <v>-42.571170784</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.2722027065999552</v>
+      </c>
+      <c r="T84">
+        <v>5.07397188260772</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.02859108320717293</v>
+      </c>
+      <c r="W84">
+        <v>0.2319724493301271</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.1681828423951349</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2412138956386962</v>
+      </c>
+      <c r="C85">
+        <v>-224.5422013892914</v>
+      </c>
+      <c r="D85">
+        <v>82.08179861070867</v>
+      </c>
+      <c r="E85">
+        <v>366.424</v>
+      </c>
+      <c r="F85">
+        <v>400.724</v>
+      </c>
+      <c r="G85">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H85">
+        <v>448.5</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>38.6</v>
+      </c>
+      <c r="K85">
+        <v>22.7</v>
+      </c>
+      <c r="L85">
+        <v>15.9</v>
+      </c>
+      <c r="M85">
+        <v>95.69289120000002</v>
+      </c>
+      <c r="N85">
+        <v>-79.79289120000001</v>
+      </c>
+      <c r="O85">
+        <v>-13.564791504</v>
+      </c>
+      <c r="P85">
+        <v>-66.22809969600002</v>
+      </c>
+      <c r="Q85">
+        <v>-43.52809969600001</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.2859322775764231</v>
+      </c>
+      <c r="T85">
+        <v>5.372440816878764</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.02824661232515879</v>
+      </c>
+      <c r="W85">
+        <v>0.2320547089767521</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.1661565430891694</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2432138956386961</v>
+      </c>
+      <c r="C86">
+        <v>-230.1732955072742</v>
+      </c>
+      <c r="D86">
+        <v>81.27870449272581</v>
+      </c>
+      <c r="E86">
+        <v>371.252</v>
+      </c>
+      <c r="F86">
+        <v>405.552</v>
+      </c>
+      <c r="G86">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H86">
+        <v>448.5</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>38.6</v>
+      </c>
+      <c r="K86">
+        <v>22.7</v>
+      </c>
+      <c r="L86">
+        <v>15.9</v>
+      </c>
+      <c r="M86">
+        <v>96.8458176</v>
+      </c>
+      <c r="N86">
+        <v>-80.9458176</v>
+      </c>
+      <c r="O86">
+        <v>-13.760788992</v>
+      </c>
+      <c r="P86">
+        <v>-67.185028608</v>
+      </c>
+      <c r="Q86">
+        <v>-44.48502860799999</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.3013780449249494</v>
+      </c>
+      <c r="T86">
+        <v>5.708218367933683</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.02791034313081167</v>
+      </c>
+      <c r="W86">
+        <v>0.2321350100603622</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.1641784890047746</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2452138956386961</v>
+      </c>
+      <c r="C87">
+        <v>-235.7888268335081</v>
+      </c>
+      <c r="D87">
+        <v>80.4911731664919</v>
+      </c>
+      <c r="E87">
+        <v>376.08</v>
+      </c>
+      <c r="F87">
+        <v>410.38</v>
+      </c>
+      <c r="G87">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H87">
+        <v>448.5</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>38.6</v>
+      </c>
+      <c r="K87">
+        <v>22.7</v>
+      </c>
+      <c r="L87">
+        <v>15.9</v>
+      </c>
+      <c r="M87">
+        <v>97.998744</v>
+      </c>
+      <c r="N87">
+        <v>-82.09874400000001</v>
+      </c>
+      <c r="O87">
+        <v>-13.95678648</v>
+      </c>
+      <c r="P87">
+        <v>-68.14195752000001</v>
+      </c>
+      <c r="Q87">
+        <v>-45.44195752</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.318883247919946</v>
+      </c>
+      <c r="T87">
+        <v>6.088766259129262</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.02758198615280212</v>
+      </c>
+      <c r="W87">
+        <v>0.2322134217067109</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.1622469773694242</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2472138956386961</v>
+      </c>
+      <c r="C88">
+        <v>-241.3892434031406</v>
+      </c>
+      <c r="D88">
+        <v>79.71875659685942</v>
+      </c>
+      <c r="E88">
+        <v>380.908</v>
+      </c>
+      <c r="F88">
+        <v>415.208</v>
+      </c>
+      <c r="G88">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H88">
+        <v>448.5</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>38.6</v>
+      </c>
+      <c r="K88">
+        <v>22.7</v>
+      </c>
+      <c r="L88">
+        <v>15.9</v>
+      </c>
+      <c r="M88">
+        <v>99.15167040000001</v>
+      </c>
+      <c r="N88">
+        <v>-83.25167040000002</v>
+      </c>
+      <c r="O88">
+        <v>-14.152783968</v>
+      </c>
+      <c r="P88">
+        <v>-69.09888643200001</v>
+      </c>
+      <c r="Q88">
+        <v>-46.39888643200001</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.3388891941999422</v>
+      </c>
+      <c r="T88">
+        <v>6.523678134781353</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.02726126538358349</v>
+      </c>
+      <c r="W88">
+        <v>0.2322900098264003</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.1603603846093146</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2492138956386961</v>
+      </c>
+      <c r="C89">
+        <v>-246.9749762168873</v>
+      </c>
+      <c r="D89">
+        <v>78.96102378311269</v>
+      </c>
+      <c r="E89">
+        <v>385.736</v>
+      </c>
+      <c r="F89">
+        <v>420.036</v>
+      </c>
+      <c r="G89">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H89">
+        <v>448.5</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>38.6</v>
+      </c>
+      <c r="K89">
+        <v>22.7</v>
+      </c>
+      <c r="L89">
+        <v>15.9</v>
+      </c>
+      <c r="M89">
+        <v>100.3045968</v>
+      </c>
+      <c r="N89">
+        <v>-84.40459680000001</v>
+      </c>
+      <c r="O89">
+        <v>-14.348781456</v>
+      </c>
+      <c r="P89">
+        <v>-70.05581534400001</v>
+      </c>
+      <c r="Q89">
+        <v>-47.35581534400001</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.3619729783691685</v>
+      </c>
+      <c r="T89">
+        <v>7.025499529764534</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.02694791750561127</v>
+      </c>
+      <c r="W89">
+        <v>0.23236483729966</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.1585171617977132</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2512138956386962</v>
+      </c>
+      <c r="C90">
+        <v>-252.5464400429774</v>
+      </c>
+      <c r="D90">
+        <v>78.21755995702262</v>
+      </c>
+      <c r="E90">
+        <v>390.564</v>
+      </c>
+      <c r="F90">
+        <v>424.864</v>
+      </c>
+      <c r="G90">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H90">
+        <v>448.5</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>38.6</v>
+      </c>
+      <c r="K90">
+        <v>22.7</v>
+      </c>
+      <c r="L90">
+        <v>15.9</v>
+      </c>
+      <c r="M90">
+        <v>101.4575232</v>
+      </c>
+      <c r="N90">
+        <v>-85.55752320000002</v>
+      </c>
+      <c r="O90">
+        <v>-14.544778944</v>
+      </c>
+      <c r="P90">
+        <v>-71.01274425600002</v>
+      </c>
+      <c r="Q90">
+        <v>-48.31274425600002</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.3889040598999327</v>
+      </c>
+      <c r="T90">
+        <v>7.610957823911579</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.02664169117032023</v>
+      </c>
+      <c r="W90">
+        <v>0.2324379641485275</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.1567158304136483</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2532138956386962</v>
+      </c>
+      <c r="C91">
+        <v>-258.1040341742162</v>
+      </c>
+      <c r="D91">
+        <v>77.48796582578382</v>
+      </c>
+      <c r="E91">
+        <v>395.392</v>
+      </c>
+      <c r="F91">
+        <v>429.692</v>
+      </c>
+      <c r="G91">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H91">
+        <v>448.5</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>38.6</v>
+      </c>
+      <c r="K91">
+        <v>22.7</v>
+      </c>
+      <c r="L91">
+        <v>15.9</v>
+      </c>
+      <c r="M91">
+        <v>102.6104496</v>
+      </c>
+      <c r="N91">
+        <v>-86.7104496</v>
+      </c>
+      <c r="O91">
+        <v>-14.740776432</v>
+      </c>
+      <c r="P91">
+        <v>-71.969673168</v>
+      </c>
+      <c r="Q91">
+        <v>-49.269673168</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.4207317017090175</v>
+      </c>
+      <c r="T91">
+        <v>8.302863080630814</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.02634234632570989</v>
+      </c>
+      <c r="W91">
+        <v>0.2325094476974205</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.1549549783865288</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2552138956386961</v>
+      </c>
+      <c r="C92">
+        <v>-263.6481431430705</v>
+      </c>
+      <c r="D92">
+        <v>76.77185685692952</v>
+      </c>
+      <c r="E92">
+        <v>400.22</v>
+      </c>
+      <c r="F92">
+        <v>434.52</v>
+      </c>
+      <c r="G92">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H92">
+        <v>448.5</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>38.6</v>
+      </c>
+      <c r="K92">
+        <v>22.7</v>
+      </c>
+      <c r="L92">
+        <v>15.9</v>
+      </c>
+      <c r="M92">
+        <v>103.763376</v>
+      </c>
+      <c r="N92">
+        <v>-87.86337600000002</v>
+      </c>
+      <c r="O92">
+        <v>-14.93677392</v>
+      </c>
+      <c r="P92">
+        <v>-72.92660208000001</v>
+      </c>
+      <c r="Q92">
+        <v>-50.22660208000001</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.4589248718799192</v>
+      </c>
+      <c r="T92">
+        <v>9.133149388693896</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.02604965358875756</v>
+      </c>
+      <c r="W92">
+        <v>0.2325793427230047</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.1532332564044562</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2572138956386962</v>
+      </c>
+      <c r="C93">
+        <v>-269.1791373974647</v>
+      </c>
+      <c r="D93">
+        <v>76.06886260253528</v>
+      </c>
+      <c r="E93">
+        <v>405.048</v>
+      </c>
+      <c r="F93">
+        <v>439.348</v>
+      </c>
+      <c r="G93">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H93">
+        <v>448.5</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>38.6</v>
+      </c>
+      <c r="K93">
+        <v>22.7</v>
+      </c>
+      <c r="L93">
+        <v>15.9</v>
+      </c>
+      <c r="M93">
+        <v>104.9163024</v>
+      </c>
+      <c r="N93">
+        <v>-89.0163024</v>
+      </c>
+      <c r="O93">
+        <v>-15.132771408</v>
+      </c>
+      <c r="P93">
+        <v>-73.883530992</v>
+      </c>
+      <c r="Q93">
+        <v>-51.183530992</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.5056054131999103</v>
+      </c>
+      <c r="T93">
+        <v>10.14794376521544</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.02576339365921077</v>
+      </c>
+      <c r="W93">
+        <v>0.2326477015941805</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.1515493744659457</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2592138956386961</v>
+      </c>
+      <c r="C94">
+        <v>-274.6973739397854</v>
+      </c>
+      <c r="D94">
+        <v>75.37862606021469</v>
+      </c>
+      <c r="E94">
+        <v>409.876</v>
+      </c>
+      <c r="F94">
+        <v>444.176</v>
+      </c>
+      <c r="G94">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H94">
+        <v>448.5</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>38.6</v>
+      </c>
+      <c r="K94">
+        <v>22.7</v>
+      </c>
+      <c r="L94">
+        <v>15.9</v>
+      </c>
+      <c r="M94">
+        <v>106.0692288</v>
+      </c>
+      <c r="N94">
+        <v>-90.16922880000001</v>
+      </c>
+      <c r="O94">
+        <v>-15.328768896</v>
+      </c>
+      <c r="P94">
+        <v>-74.84045990400001</v>
+      </c>
+      <c r="Q94">
+        <v>-52.14045990400001</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.5639560898498992</v>
+      </c>
+      <c r="T94">
+        <v>11.41643673586738</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.02548335677161065</v>
+      </c>
+      <c r="W94">
+        <v>0.2327145744029394</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.1499020986565333</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2612138956386962</v>
+      </c>
+      <c r="C95">
+        <v>-280.2031969314087</v>
+      </c>
+      <c r="D95">
+        <v>74.7008030685913</v>
+      </c>
+      <c r="E95">
+        <v>414.704</v>
+      </c>
+      <c r="F95">
+        <v>449.004</v>
+      </c>
+      <c r="G95">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H95">
+        <v>448.5</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>38.6</v>
+      </c>
+      <c r="K95">
+        <v>22.7</v>
+      </c>
+      <c r="L95">
+        <v>15.9</v>
+      </c>
+      <c r="M95">
+        <v>107.2221552</v>
+      </c>
+      <c r="N95">
+        <v>-91.3221552</v>
+      </c>
+      <c r="O95">
+        <v>-15.524766384</v>
+      </c>
+      <c r="P95">
+        <v>-75.79738881599999</v>
+      </c>
+      <c r="Q95">
+        <v>-53.09738881599999</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.638978388399885</v>
+      </c>
+      <c r="T95">
+        <v>13.04735626956272</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.0252093421826686</v>
+      </c>
+      <c r="W95">
+        <v>0.2327800090867788</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.1482902481333448</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2632138956386961</v>
+      </c>
+      <c r="C96">
+        <v>-285.6969382649032</v>
+      </c>
+      <c r="D96">
+        <v>74.0350617350969</v>
+      </c>
+      <c r="E96">
+        <v>419.532</v>
+      </c>
+      <c r="F96">
+        <v>453.8320000000001</v>
+      </c>
+      <c r="G96">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H96">
+        <v>448.5</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>38.6</v>
+      </c>
+      <c r="K96">
+        <v>22.7</v>
+      </c>
+      <c r="L96">
+        <v>15.9</v>
+      </c>
+      <c r="M96">
+        <v>108.3750816</v>
+      </c>
+      <c r="N96">
+        <v>-92.47508160000001</v>
+      </c>
+      <c r="O96">
+        <v>-15.720763872</v>
+      </c>
+      <c r="P96">
+        <v>-76.754317728</v>
+      </c>
+      <c r="Q96">
+        <v>-54.054317728</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.7390081197998659</v>
+      </c>
+      <c r="T96">
+        <v>15.22191564782317</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.02494115769136361</v>
+      </c>
+      <c r="W96">
+        <v>0.2328440515433024</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.146712692302139</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2652138956386962</v>
+      </c>
+      <c r="C97">
+        <v>-291.1789181059041</v>
+      </c>
+      <c r="D97">
+        <v>73.38108189409597</v>
+      </c>
+      <c r="E97">
+        <v>424.36</v>
+      </c>
+      <c r="F97">
+        <v>458.66</v>
+      </c>
+      <c r="G97">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H97">
+        <v>448.5</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>38.6</v>
+      </c>
+      <c r="K97">
+        <v>22.7</v>
+      </c>
+      <c r="L97">
+        <v>15.9</v>
+      </c>
+      <c r="M97">
+        <v>109.528008</v>
+      </c>
+      <c r="N97">
+        <v>-93.62800800000002</v>
+      </c>
+      <c r="O97">
+        <v>-15.91676136</v>
+      </c>
+      <c r="P97">
+        <v>-77.71124664000001</v>
+      </c>
+      <c r="Q97">
+        <v>-55.01124664000001</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>0.8790497437598397</v>
+      </c>
+      <c r="T97">
+        <v>18.26629877738782</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.02467861918934926</v>
+      </c>
+      <c r="W97">
+        <v>0.2329067457375834</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.1451683481726427</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2672138956386961</v>
+      </c>
+      <c r="C98">
+        <v>-296.6494454065212</v>
+      </c>
+      <c r="D98">
+        <v>72.7385545934788</v>
+      </c>
+      <c r="E98">
+        <v>429.188</v>
+      </c>
+      <c r="F98">
+        <v>463.488</v>
+      </c>
+      <c r="G98">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H98">
+        <v>448.5</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>38.6</v>
+      </c>
+      <c r="K98">
+        <v>22.7</v>
+      </c>
+      <c r="L98">
+        <v>15.9</v>
+      </c>
+      <c r="M98">
+        <v>110.6809344</v>
+      </c>
+      <c r="N98">
+        <v>-94.78093440000001</v>
+      </c>
+      <c r="O98">
+        <v>-16.112758848</v>
+      </c>
+      <c r="P98">
+        <v>-78.66817555200001</v>
+      </c>
+      <c r="Q98">
+        <v>-55.96817555200001</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.089112179699797</v>
+      </c>
+      <c r="T98">
+        <v>22.83287347173471</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.02442155023946021</v>
+      </c>
+      <c r="W98">
+        <v>0.2329681338028169</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.1436561778791777</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2692138956386961</v>
+      </c>
+      <c r="C99">
+        <v>-302.1088183920076</v>
+      </c>
+      <c r="D99">
+        <v>72.10718160799239</v>
+      </c>
+      <c r="E99">
+        <v>434.016</v>
+      </c>
+      <c r="F99">
+        <v>468.316</v>
+      </c>
+      <c r="G99">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H99">
+        <v>448.5</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>38.6</v>
+      </c>
+      <c r="K99">
+        <v>22.7</v>
+      </c>
+      <c r="L99">
+        <v>15.9</v>
+      </c>
+      <c r="M99">
+        <v>111.8338608</v>
+      </c>
+      <c r="N99">
+        <v>-95.93386079999999</v>
+      </c>
+      <c r="O99">
+        <v>-16.308756336</v>
+      </c>
+      <c r="P99">
+        <v>-79.62510446399999</v>
+      </c>
+      <c r="Q99">
+        <v>-56.92510446399999</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.439216239599729</v>
+      </c>
+      <c r="T99">
+        <v>30.44383129564629</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.02416978168029052</v>
+      </c>
+      <c r="W99">
+        <v>0.2330282561347466</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.1421751863546502</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2712138956386962</v>
+      </c>
+      <c r="C100">
+        <v>-307.5573250223004</v>
+      </c>
+      <c r="D100">
+        <v>71.48667497769959</v>
+      </c>
+      <c r="E100">
+        <v>438.844</v>
+      </c>
+      <c r="F100">
+        <v>473.144</v>
+      </c>
+      <c r="G100">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H100">
+        <v>448.5</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>38.6</v>
+      </c>
+      <c r="K100">
+        <v>22.7</v>
+      </c>
+      <c r="L100">
+        <v>15.9</v>
+      </c>
+      <c r="M100">
+        <v>112.9867872</v>
+      </c>
+      <c r="N100">
+        <v>-97.0867872</v>
+      </c>
+      <c r="O100">
+        <v>-16.504753824</v>
+      </c>
+      <c r="P100">
+        <v>-80.582033376</v>
+      </c>
+      <c r="Q100">
+        <v>-57.882033376</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.139424359399594</v>
+      </c>
+      <c r="T100">
+        <v>45.66574694346943</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.02392315125498143</v>
+      </c>
+      <c r="W100">
+        <v>0.2330871514803105</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.1407244191469497</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2732138956386961</v>
+      </c>
+      <c r="C101">
+        <v>-312.9952434299351</v>
+      </c>
+      <c r="D101">
+        <v>70.87675657006488</v>
+      </c>
+      <c r="E101">
+        <v>443.672</v>
+      </c>
+      <c r="F101">
+        <v>477.972</v>
+      </c>
+      <c r="G101">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H101">
+        <v>448.5</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>38.6</v>
+      </c>
+      <c r="K101">
+        <v>22.7</v>
+      </c>
+      <c r="L101">
+        <v>15.9</v>
+      </c>
+      <c r="M101">
+        <v>114.1397136</v>
+      </c>
+      <c r="N101">
+        <v>-98.23971360000002</v>
+      </c>
+      <c r="O101">
+        <v>-16.700751312</v>
+      </c>
+      <c r="P101">
+        <v>-81.53896228800001</v>
+      </c>
+      <c r="Q101">
+        <v>-58.838962288</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>4.240048718799188</v>
+      </c>
+      <c r="T101">
+        <v>91.33149388693886</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.02368150326250687</v>
+      </c>
+      <c r="W101">
+        <v>0.2331448570209134</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.1393029603676874</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
